--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -28,13 +28,13 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
-    <numFmt numFmtId="167" formatCode="+0.00%;-0.00%"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="168" formatCode="+0.00%;-0.00%"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,15 +126,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00660000"/>
       <sz val="11"/>
     </font>
@@ -172,7 +163,7 @@
       <color rgb="00006600"/>
     </font>
     <font>
-      <color rgb="00CC0000"/>
+      <color rgb="00CC6600"/>
     </font>
     <font>
       <i val="1"/>
@@ -207,9 +198,6 @@
       <b val="1"/>
       <color rgb="00404040"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00CC6600"/>
     </font>
     <font>
       <color rgb="000563C1"/>
@@ -323,17 +311,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -424,12 +412,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -438,58 +428,54 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="28" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="30" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="20" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="20" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -509,7 +495,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -540,45 +526,43 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1191,39 +1175,39 @@
         <v/>
       </c>
       <c r="K5" s="10">
-        <f>K4*0.2593</f>
+        <f>K4*0.2850</f>
         <v/>
       </c>
       <c r="L5" s="10">
-        <f>L4*0.2593</f>
+        <f>L4*0.2750</f>
         <v/>
       </c>
       <c r="M5" s="10">
-        <f>M4*0.2593</f>
+        <f>M4*0.2750</f>
         <v/>
       </c>
       <c r="N5" s="10">
-        <f>N4*0.2593</f>
+        <f>N4*0.2750</f>
         <v/>
       </c>
       <c r="O5" s="10">
-        <f>O4*0.2593</f>
+        <f>O4*0.2750</f>
         <v/>
       </c>
       <c r="P5" s="10">
-        <f>P4*0.2593</f>
+        <f>P4*0.2750</f>
         <v/>
       </c>
       <c r="Q5" s="10">
-        <f>Q4*0.2593</f>
+        <f>Q4*0.2750</f>
         <v/>
       </c>
       <c r="R5" s="10">
-        <f>R4*0.2593</f>
+        <f>R4*0.2750</f>
         <v/>
       </c>
       <c r="S5" s="10">
-        <f>S4*0.2593</f>
+        <f>S4*0.2750</f>
         <v/>
       </c>
     </row>
@@ -1903,61 +1887,67 @@
           <t>EPS</t>
         </is>
       </c>
-      <c r="B16" s="131" t="n">
+      <c r="B16" s="129" t="n">
         <v>0.78</v>
       </c>
-      <c r="D16" s="131" t="n">
+      <c r="C16" s="129" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D16" s="129" t="n">
         <v>0.76</v>
       </c>
-      <c r="E16" s="131" t="n">
+      <c r="E16" s="129" t="n">
         <v>1.08</v>
       </c>
-      <c r="F16" s="131" t="n">
+      <c r="F16" s="129" t="n">
         <v>1.3</v>
       </c>
-      <c r="H16" s="131" t="n">
+      <c r="G16" s="129" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H16" s="129" t="n">
         <v>2.39</v>
       </c>
-      <c r="I16" s="131" t="n">
+      <c r="I16" s="129" t="n">
         <v>2.46</v>
       </c>
-      <c r="J16" s="132">
+      <c r="J16" s="130">
         <f>IF(J17&lt;&gt;0,J15/J17,"")</f>
         <v/>
       </c>
-      <c r="K16" s="132">
+      <c r="K16" s="130">
         <f>IF(K17&lt;&gt;0,K15/K17,"")</f>
         <v/>
       </c>
-      <c r="L16" s="132">
+      <c r="L16" s="130">
         <f>IF(L17&lt;&gt;0,L15/L17,"")</f>
         <v/>
       </c>
-      <c r="M16" s="132">
+      <c r="M16" s="130">
         <f>IF(M17&lt;&gt;0,M15/M17,"")</f>
         <v/>
       </c>
-      <c r="N16" s="132">
+      <c r="N16" s="130">
         <f>IF(N17&lt;&gt;0,N15/N17,"")</f>
         <v/>
       </c>
-      <c r="O16" s="132">
+      <c r="O16" s="130">
         <f>IF(O17&lt;&gt;0,O15/O17,"")</f>
         <v/>
       </c>
-      <c r="P16" s="132">
+      <c r="P16" s="130">
         <f>IF(P17&lt;&gt;0,P15/P17,"")</f>
         <v/>
       </c>
-      <c r="Q16" s="132">
+      <c r="Q16" s="130">
         <f>IF(Q17&lt;&gt;0,Q15/Q17,"")</f>
         <v/>
       </c>
-      <c r="R16" s="132">
+      <c r="R16" s="130">
         <f>IF(R17&lt;&gt;0,R15/R17,"")</f>
         <v/>
       </c>
-      <c r="S16" s="132">
+      <c r="S16" s="130">
         <f>IF(S17&lt;&gt;0,S15/S17,"")</f>
         <v/>
       </c>
@@ -1987,43 +1977,43 @@
         <v>24285</v>
       </c>
       <c r="J17" s="10">
-        <f>24285.0-(J15*0.9*0.55/230.36)</f>
+        <f>24285.0-(J15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="K17" s="10">
-        <f>J17-(K15*0.9*0.55/230.36)</f>
+        <f>J17-(K15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="L17" s="10">
-        <f>K17-(L15*0.9*0.55/230.36)</f>
+        <f>K17-(L15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="M17" s="10">
-        <f>L17-(M15*0.9*0.55/230.36)</f>
+        <f>L17-(M15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="N17" s="10">
-        <f>M17-(N15*0.9*0.55/230.36)</f>
+        <f>M17-(N15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="O17" s="10">
-        <f>N17-(O15*0.9*0.55/230.36)</f>
+        <f>N17-(O15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="P17" s="10">
-        <f>O17-(P15*0.9*0.55/230.36)</f>
+        <f>O17-(P15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="Q17" s="10">
-        <f>P17-(Q15*0.9*0.55/230.36)</f>
+        <f>P17-(Q15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="R17" s="10">
-        <f>Q17-(R15*0.9*0.55/230.36)</f>
+        <f>Q17-(R15*0.9*0.55/221.30)</f>
         <v/>
       </c>
       <c r="S17" s="10">
-        <f>R17-(S15*0.9*0.55/230.36)</f>
+        <f>R17-(S15*0.9*0.55/221.30)</f>
         <v/>
       </c>
     </row>
@@ -3060,19 +3050,19 @@
           <t>EPS</t>
         </is>
       </c>
-      <c r="B49" s="133">
+      <c r="B49" s="131">
         <f>D16+E16+F16+G16</f>
         <v/>
       </c>
-      <c r="C49" s="134">
+      <c r="C49" s="132">
         <f>H16+I16+J16+K16</f>
         <v/>
       </c>
-      <c r="D49" s="134">
+      <c r="D49" s="132">
         <f>L16+M16+N16+O16</f>
         <v/>
       </c>
-      <c r="E49" s="134">
+      <c r="E49" s="132">
         <f>P16+Q16+R16+S16</f>
         <v/>
       </c>
@@ -3251,7 +3241,7 @@
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
-          <t>Share discipline + cash runway ($Ms; shares in millions). Historical quarters only — raw parsed values, no forecasts.</t>
+          <t>Share discipline + cash runway ($Ms; shares in millions). Historical quarters only — reported values, no forecasts.</t>
         </is>
       </c>
     </row>
@@ -3303,22 +3293,22 @@
           <t>Diluted Shares (M)</t>
         </is>
       </c>
-      <c r="B4" s="159" t="n">
+      <c r="B4" s="157" t="n">
         <v>24774</v>
       </c>
-      <c r="D4" s="159" t="n">
+      <c r="D4" s="157" t="n">
         <v>24611</v>
       </c>
-      <c r="E4" s="159" t="n">
+      <c r="E4" s="157" t="n">
         <v>24532</v>
       </c>
-      <c r="F4" s="159" t="n">
+      <c r="F4" s="157" t="n">
         <v>24483</v>
       </c>
-      <c r="H4" s="159" t="n">
+      <c r="H4" s="157" t="n">
         <v>24391</v>
       </c>
-      <c r="I4" s="159" t="n">
+      <c r="I4" s="157" t="n">
         <v>24285</v>
       </c>
     </row>
@@ -3353,28 +3343,28 @@
           <t>SBC ($M)</t>
         </is>
       </c>
-      <c r="B6" s="159" t="n">
+      <c r="B6" s="157" t="n">
         <v>1252</v>
       </c>
-      <c r="C6" s="159" t="n">
+      <c r="C6" s="157" t="n">
         <v>1321</v>
       </c>
-      <c r="D6" s="159" t="n">
+      <c r="D6" s="157" t="n">
         <v>1474</v>
       </c>
-      <c r="E6" s="159" t="n">
+      <c r="E6" s="157" t="n">
         <v>1625</v>
       </c>
-      <c r="F6" s="159" t="n">
+      <c r="F6" s="157" t="n">
         <v>1654</v>
       </c>
-      <c r="G6" s="159" t="n">
+      <c r="G6" s="157" t="n">
         <v>1633</v>
       </c>
-      <c r="H6" s="159" t="n">
+      <c r="H6" s="157" t="n">
         <v>1928</v>
       </c>
-      <c r="I6" s="159" t="n">
+      <c r="I6" s="157" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3416,28 +3406,28 @@
           <t>Cash ($M)</t>
         </is>
       </c>
-      <c r="B9" s="159" t="n">
+      <c r="B9" s="157" t="n">
         <v>9107</v>
       </c>
-      <c r="C9" s="159" t="n">
+      <c r="C9" s="157" t="n">
         <v>8589</v>
       </c>
-      <c r="D9" s="159" t="n">
+      <c r="D9" s="157" t="n">
         <v>15234</v>
       </c>
-      <c r="E9" s="159" t="n">
+      <c r="E9" s="157" t="n">
         <v>11639</v>
       </c>
-      <c r="F9" s="159" t="n">
+      <c r="F9" s="157" t="n">
         <v>11486</v>
       </c>
-      <c r="G9" s="159" t="n">
+      <c r="G9" s="157" t="n">
         <v>10605</v>
       </c>
-      <c r="H9" s="159" t="n">
+      <c r="H9" s="157" t="n">
         <v>13237</v>
       </c>
-      <c r="I9" s="159" t="n">
+      <c r="I9" s="157" t="n">
         <v>22443</v>
       </c>
     </row>
@@ -3447,28 +3437,28 @@
           <t>Quarterly FCF ($M)</t>
         </is>
       </c>
-      <c r="B10" s="159" t="n">
+      <c r="B10" s="157" t="n">
         <v>16814</v>
       </c>
-      <c r="C10" s="159" t="n">
+      <c r="C10" s="157" t="n">
         <v>15552</v>
       </c>
-      <c r="D10" s="159" t="n">
+      <c r="D10" s="157" t="n">
         <v>26187</v>
       </c>
-      <c r="E10" s="159" t="n">
+      <c r="E10" s="157" t="n">
         <v>13470</v>
       </c>
-      <c r="F10" s="159" t="n">
+      <c r="F10" s="157" t="n">
         <v>22115</v>
       </c>
-      <c r="G10" s="159" t="n">
+      <c r="G10" s="157" t="n">
         <v>34904</v>
       </c>
-      <c r="H10" s="159" t="n">
+      <c r="H10" s="157" t="n">
         <v>48587</v>
       </c>
-      <c r="I10" s="159" t="n">
+      <c r="I10" s="157" t="n">
         <v>21400</v>
       </c>
     </row>
@@ -3486,7 +3476,7 @@
           <t>TTM FCF ($M)</t>
         </is>
       </c>
-      <c r="B13" s="152" t="n">
+      <c r="B13" s="151" t="n">
         <v>127006</v>
       </c>
     </row>
@@ -3496,7 +3486,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B14" s="120" t="inlineStr">
+      <c r="B14" s="118" t="inlineStr">
         <is>
           <t>Self-funding</t>
         </is>
@@ -3525,7 +3515,7 @@
     <row r="18">
       <c r="A18" s="33" t="inlineStr">
         <is>
-          <t>count already reflects buybacks. Audit flags net dilution: YELLOW &gt; 4%/yr, RED &gt; 8%/yr</t>
+          <t>count already reflects buybacks.</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3592,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Input quarterly segment estimates in yellow cells ($Ms). Q4 columns show annual 10-K totals as reference. | Estimates: Q2 FY27 8-K: Q3 guide $108.0B +/-2%. Segments re-cut to the FY27 customer-type taxonomy; split held at the Q2 FY27 ACTUAL mix rather than extrapolating the 2-quarter AICIE share drift (too thin to trend).</t>
+          <t>Q4 columns show annual 10-K totals as reference. | Estimates: Q2 FY27 8-K: Q3 guide $108.0B +/-2%. Segments re-cut to the FY27 customer-type taxonomy; split held at the Q2 FY27 ACTUAL mix rather than extrapolating the 2-quarter AICIE share drift (too thin to trend).</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3706,7 @@
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>Hyperscale</t>
+          <t xml:space="preserve">  Hyperscale</t>
         </is>
       </c>
       <c r="B4" s="9" t="n"/>
@@ -3742,16 +3732,16 @@
         <v>60960</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>63710</v>
+        <v>70535.39999999999</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>66898</v>
+        <v>81614.89999999999</v>
       </c>
       <c r="N4" s="10" t="n">
-        <v>69569</v>
+        <v>94434.7</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>72348</v>
+        <v>109268.2</v>
       </c>
       <c r="P4" s="10" t="n"/>
       <c r="Q4" s="10" t="n"/>
@@ -3773,7 +3763,7 @@
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>AI Clouds, Industrial, &amp; Enterprise</t>
+          <t xml:space="preserve">  AI Clouds, Industrial, &amp; Enterprise</t>
         </is>
       </c>
       <c r="B5" s="9" t="n"/>
@@ -3799,16 +3789,16 @@
         <v>50451</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>52727</v>
+        <v>58375.8</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>55366</v>
+        <v>67545.39999999999</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>57576</v>
+        <v>78155.3</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>59876</v>
+        <v>90431.89999999999</v>
       </c>
       <c r="P5" s="10" t="n"/>
       <c r="Q5" s="10" t="n"/>
@@ -3830,7 +3820,7 @@
     <row r="6">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t xml:space="preserve">  Compute</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
@@ -3875,7 +3865,7 @@
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>Networking</t>
+          <t xml:space="preserve">  Networking</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
@@ -4414,7 +4404,7 @@
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
-          <t>Edit yellow cells to override Bear/Base/Bull segment revenue ($M). Changes persist across refresh.</t>
+          <t>Bear / Base / Bull segment revenue ($M). Bands are set for FY28 only - FY27 is largely closed (two quarters printed, one guided) and FY29 carries no segment estimates, so those columns are blank. The DCF takes the FY28 band, scaled back in FY27 by the share of that year still open; after FY28 each scenario follows the recovery path its narrative states.</t>
         </is>
       </c>
     </row>
@@ -4490,20 +4480,20 @@
     <row r="6">
       <c r="A6" s="38" t="inlineStr">
         <is>
-          <t>Hyperscale</t>
+          <t xml:space="preserve">  Hyperscale</t>
         </is>
       </c>
       <c r="B6" s="39" t="n"/>
       <c r="C6" s="39" t="n"/>
       <c r="D6" s="39" t="n"/>
       <c r="E6" s="39" t="n">
-        <v>172263.9</v>
+        <v>355853</v>
       </c>
       <c r="F6" s="39" t="n">
-        <v>272525</v>
+        <v>355853</v>
       </c>
       <c r="G6" s="39" t="n">
-        <v>372786.1</v>
+        <v>422539</v>
       </c>
       <c r="H6" s="39" t="n"/>
       <c r="I6" s="39" t="n"/>
@@ -4512,20 +4502,20 @@
     <row r="7">
       <c r="A7" s="38" t="inlineStr">
         <is>
-          <t>AI Clouds, Industrial, &amp; Enterprise</t>
+          <t xml:space="preserve">  AI Clouds, Industrial, &amp; Enterprise</t>
         </is>
       </c>
       <c r="B7" s="39" t="n"/>
       <c r="C7" s="39" t="n"/>
       <c r="D7" s="39" t="n"/>
       <c r="E7" s="39" t="n">
-        <v>134145.8</v>
+        <v>294508</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>225545</v>
+        <v>294508</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>316944.2</v>
+        <v>349699</v>
       </c>
       <c r="H7" s="39" t="n"/>
       <c r="I7" s="39" t="n"/>
@@ -4534,7 +4524,7 @@
     <row r="8">
       <c r="A8" s="38" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t xml:space="preserve">  Compute</t>
         </is>
       </c>
       <c r="B8" s="39" t="n"/>
@@ -4550,7 +4540,7 @@
     <row r="9">
       <c r="A9" s="38" t="inlineStr">
         <is>
-          <t>Networking</t>
+          <t xml:space="preserve">  Networking</t>
         </is>
       </c>
       <c r="B9" s="39" t="n"/>
@@ -4616,13 +4606,13 @@
       <c r="C11" s="39" t="n"/>
       <c r="D11" s="39" t="n"/>
       <c r="E11" s="39" t="n">
-        <v>36570.7</v>
+        <v>40272</v>
       </c>
       <c r="F11" s="39" t="n">
         <v>40272</v>
       </c>
       <c r="G11" s="39" t="n">
-        <v>43973.3</v>
+        <v>40272</v>
       </c>
       <c r="H11" s="39" t="n"/>
       <c r="I11" s="39" t="n"/>
@@ -4759,7 +4749,11 @@
           <t>Bear thesis:</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n"/>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>HYPERSCALERS DIGEST IN CY28. NVIDIA guided FY28 revenue growth of about 70% on the call - its first year-ahead guide, backed by customer forecasts and $279B of supply commitments - so this bear lets FY28 land on the guide ($690.6B). The digestion comes the year AFTER the build, as in 2023 when top-4 hyperscaler capex fell about 4% after the 2022 build: FY29 revenue is flat instead of the base's +23.1%, then growth returns to the base rates and the lost level is never recovered ( bear 'stall:1'), so revenue ends about 19% below base. Goldman and UBS already model 2028 hyperscaler capex growth slowing to +12-17%; this bear takes it to zero. MARGIN FALLS WITH REVENUE: from the stall year (FY29) operating margin is 58.7% instead of 65.2%. Every NVDA downturn compressed margin in the year revenue stalled (FY23, flat revenue: gross margin 64.9% to 56.9%), and 58.7% is also where JPM's custom-silicon unit-share path lands as roughly 13% Data Center price erosion, so the bear carries both the volume risk and the price risk. Superseded : the CY27 stall (FY28 flat at $415.9B), which against the +70% guide had become a -40% miss. What would tell us: hyperscaler CY27 capex guides (Jan-Feb 2027) well under Goldman's +50%, CY28 guides (Jan-Feb 2028) near flat, then two straight quarters of falling NVDA revenue.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="inlineStr">
@@ -4767,32 +4761,24 @@
           <t>Bull thesis:</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n"/>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>CUSTOMER DEMAND IS MET. On the call CFO Colette Kress said customer forecasts 'point to our growth doubling next year' and that NVIDIA is supply constrained; the guide is about 70%. This bull lets supply catch up: FY28 revenue reaches 2x the base case's FY27 ($406.3B) = $812.5B, +17.6% over the $690.6B guided base (the bull's own FY27 is $424.2B, because the step is carried back onto FY27's one open quarter, so its own FY28 growth is +91.5%), with Data Center carrying the step and Edge Computing at its base $40.3B. Doubling is a one-time LEVEL gain: after FY28 the bull grows at the base rates ( bull 'base'). It supersedes the 58%-accelerator-share bull (FY28 $654.9B), which sat below the guided base. What would tell us: supply commitments rising again and quarterly revenue ramping faster than the ~15% a quarter the guide implies.</t>
+        </is>
+      </c>
     </row>
     <row r="22"/>
     <row r="23">
       <c r="A23" s="33" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>1. Yellow cells = your overrides for each scenario's segment revenue</t>
-        </is>
-      </c>
+      <c r="A24" s="33" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>2. Defaults from drivers section (Base) and segment volatility (Bear/Bull)</t>
-        </is>
-      </c>
+      <c r="A25" s="33" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>3. These values flow into DCF Bear/Base/Bull scenarios on next refresh</t>
-        </is>
-      </c>
+      <c r="A26" s="33" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="33" t="n"/>
@@ -4812,7 +4798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4823,6 +4809,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4847,7 +4835,7 @@
         </is>
       </c>
       <c r="B4" s="47" t="n">
-        <v>0.1146510108547472</v>
+        <v>0.1186991999103706</v>
       </c>
     </row>
     <row r="5">
@@ -4937,748 +4925,839 @@
         </is>
       </c>
       <c r="B13" s="47" t="n">
-        <v>-0.008642512593634551</v>
-      </c>
-    </row>
-    <row r="14"/>
+        <v>-0.008996336095516673</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>First Period: Years Until Its Cash</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="n">
+        <v>0.2957</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>First Period: Share Still to Come</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="n">
+        <v>0.5623</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
+        <is>
+          <t>Year 1 (FY27) counts only the 56% of its cash still to come (2 of 4 quarters still open), discounted to the fiscal year-end; each later year arrives one year after the one before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>WACC BUILD</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t>Risk-Free Rate (Rf)</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
-        <v>0.0478</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="B19" s="50" t="n">
+        <v>0.0519</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Equity Risk Premium (ERP)</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
-        <v>0.0414</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="B20" s="50" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>Raw Beta</t>
         </is>
       </c>
-      <c r="B18" s="50" t="n">
-        <v>1.887</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="B21" s="51" t="n">
+        <v>1.8244</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr">
         <is>
           <t>Blume-Adjusted Beta (Own)</t>
         </is>
       </c>
-      <c r="B19" s="50" t="n">
-        <v>1.591333333333333</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="B22" s="51" t="n">
+        <v>1.5496</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t>Peer Blume Beta</t>
         </is>
       </c>
-      <c r="B20" s="50" t="n">
-        <v>1.660464748204461</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="B23" s="51" t="n">
+        <v>1.654416368755674</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
         <is>
           <t>Blended Beta</t>
         </is>
       </c>
-      <c r="B21" s="50" t="n">
-        <v>1.625899040768897</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="B24" s="51" t="n">
+        <v>1.602008184377837</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
         <is>
           <t>Cost of Equity (Ke = Rf + β×ERP)</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n">
-        <v>0.1151122202878323</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="B25" s="50" t="n">
+        <v>0.1191843437438692</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
         <is>
           <t>Pre-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B23" s="49" t="n">
-        <v>0.0478</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+      <c r="B26" s="50" t="n">
+        <v>0.0519</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t>After-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B24" s="49" t="n">
-        <v>0.037762</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="B27" s="50" t="n">
+        <v>0.041001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
         <is>
           <t>Equity Weight (E/V)</t>
         </is>
       </c>
-      <c r="B25" s="49" t="n">
-        <v>0.9940373869477183</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="B28" s="50" t="n">
+        <v>0.9937947929793342</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr">
         <is>
           <t>Debt Weight (D/V)</t>
         </is>
       </c>
-      <c r="B26" s="49" t="n">
-        <v>0.00596261305228174</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="B29" s="50" t="n">
+        <v>0.006205207020665895</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="inlineStr">
         <is>
           <t>→ WACC = (E/V)×Ke + (D/V)×Kd×(1-t)</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n">
-        <v>0.1146510108547472</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="B30" s="50" t="n">
+        <v>0.1186991999103706</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
         <is>
           <t>Beta:</t>
         </is>
       </c>
-      <c r="B28" s="48" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>Peer-blended (curated)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="48" t="n"/>
-      <c r="B29" s="48" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="49" t="n"/>
+      <c r="B32" s="49" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Revenue Growth Rates:</t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="B32" s="47" t="n">
-        <v>0.3409</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="B33" s="47" t="n">
-        <v>0.3251</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="B34" s="47" t="n">
-        <v>0.2499</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Year 4</t>
+          <t xml:space="preserve">  Year 1</t>
         </is>
       </c>
       <c r="B35" s="47" t="n">
-        <v>0.1102</v>
+        <v>0.3409</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Year 5</t>
+          <t xml:space="preserve">  Year 2</t>
         </is>
       </c>
       <c r="B36" s="47" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="37"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year 3</t>
+        </is>
+      </c>
+      <c r="B37" s="47" t="n">
+        <v>0.2305</v>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>TTM FINANCIALS ($M)</t>
-        </is>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year 4</t>
+        </is>
+      </c>
+      <c r="B38" s="47" t="n">
+        <v>0.1358</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B39" s="51" t="n">
-        <v>302969</v>
+          <t xml:space="preserve">  Year 5</t>
+        </is>
+      </c>
+      <c r="B39" s="47" t="n">
+        <v>0.0955</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Operating Income</t>
-        </is>
-      </c>
-      <c r="B40" s="51" t="n">
-        <v>197579</v>
+          <t xml:space="preserve">  Year 6</t>
+        </is>
+      </c>
+      <c r="B40" s="47" t="n">
+        <v>0.0564</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="B41" s="51" t="n">
-        <v>192879</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Stock-Based Comp</t>
-        </is>
-      </c>
-      <c r="B42" s="51" t="n">
-        <v>7241</v>
-      </c>
-    </row>
+          <t xml:space="preserve">  Year 7</t>
+        </is>
+      </c>
+      <c r="B41" s="47" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Share Buybacks</t>
-        </is>
-      </c>
-      <c r="B43" s="51" t="n">
-        <v>55315</v>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>TTM FINANCIALS ($M)</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CFFO</t>
-        </is>
-      </c>
-      <c r="B44" s="51" t="n">
-        <v>134360</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B44" s="52" t="n">
+        <v>302969</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CapEx</t>
-        </is>
-      </c>
-      <c r="B45" s="51" t="n">
-        <v>7354</v>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B45" s="52" t="n">
+        <v>197579</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="B46" s="51" t="n">
-        <v>22443</v>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B46" s="52" t="n">
+        <v>192879</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Debt</t>
-        </is>
-      </c>
-      <c r="B47" s="51" t="n">
-        <v>33366</v>
+          <t>Stock-Based Comp</t>
+        </is>
+      </c>
+      <c r="B47" s="52" t="n">
+        <v>7241</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Shares Outstanding</t>
-        </is>
-      </c>
-      <c r="B48" s="51" t="n">
-        <v>24285000000</v>
-      </c>
-    </row>
-    <row r="49"/>
+          <t>Share Buybacks</t>
+        </is>
+      </c>
+      <c r="B48" s="52" t="n">
+        <v>55315</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CFFO</t>
+        </is>
+      </c>
+      <c r="B49" s="52" t="n">
+        <v>134360</v>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>PROJECTED FREE CASH FLOW ($M)</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="B50" s="52" t="n">
+        <v>7354</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr"/>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>TTM</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B51" s="52" t="n">
+        <v>22443</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
-        </is>
-      </c>
-      <c r="C52" s="49">
-        <f>$B$32</f>
-        <v/>
-      </c>
-      <c r="D52" s="49">
-        <f>$B$33</f>
-        <v/>
-      </c>
-      <c r="E52" s="49">
-        <f>$B$34</f>
-        <v/>
-      </c>
-      <c r="F52" s="49">
-        <f>$B$35</f>
-        <v/>
-      </c>
-      <c r="G52" s="49">
-        <f>$B$36</f>
-        <v/>
+          <t>Short-Term Investments</t>
+        </is>
+      </c>
+      <c r="B52" s="52" t="n">
+        <v>34143</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B53" s="51" t="n">
-        <v>302969</v>
-      </c>
-      <c r="C53" s="51">
-        <f>B53*(1+C52)</f>
-        <v/>
-      </c>
-      <c r="D53" s="51">
-        <f>C53*(1+D52)</f>
-        <v/>
-      </c>
-      <c r="E53" s="51">
-        <f>D53*(1+E52)</f>
-        <v/>
-      </c>
-      <c r="F53" s="51">
-        <f>E53*(1+F52)</f>
-        <v/>
-      </c>
-      <c r="G53" s="51">
-        <f>F53*(1+G52)</f>
-        <v/>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="B53" s="52" t="n">
+        <v>33366</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Operating Margin</t>
-        </is>
-      </c>
-      <c r="B54" s="49" t="n">
-        <v>0.6521426284537362</v>
-      </c>
-      <c r="C54" s="47" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="D54" s="47" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="E54" s="47" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="F54" s="47" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="G54" s="47" t="n">
-        <v>0.6521</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Operating Income</t>
-        </is>
-      </c>
-      <c r="B55" s="51" t="n">
-        <v>197579</v>
-      </c>
-      <c r="C55" s="51">
-        <f>C53*C54</f>
-        <v/>
-      </c>
-      <c r="D55" s="51">
-        <f>D53*D54</f>
-        <v/>
-      </c>
-      <c r="E55" s="51">
-        <f>E53*E54</f>
-        <v/>
-      </c>
-      <c r="F55" s="51">
-        <f>F53*F54</f>
-        <v/>
-      </c>
-      <c r="G55" s="51">
-        <f>G53*G54</f>
-        <v/>
-      </c>
-    </row>
+          <t>Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="B54" s="52" t="n">
+        <v>24285000000</v>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NOPAT</t>
-        </is>
-      </c>
-      <c r="C56" s="51">
-        <f>C55*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="D56" s="51">
-        <f>D55*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="E56" s="51">
-        <f>E55*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="F56" s="51">
-        <f>F55*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="G56" s="51">
-        <f>G55*(1-$B$6)</f>
-        <v/>
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>PROJECTED FREE CASH FLOW ($M)</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C57" s="51">
-        <f>C53*$B$10</f>
-        <v/>
-      </c>
-      <c r="D57" s="51">
-        <f>D53*$B$10</f>
-        <v/>
-      </c>
-      <c r="E57" s="51">
-        <f>E53*$B$10</f>
-        <v/>
-      </c>
-      <c r="F57" s="51">
-        <f>F53*$B$10</f>
-        <v/>
-      </c>
-      <c r="G57" s="51">
-        <f>G53*$B$10</f>
-        <v/>
+      <c r="A57" s="1" t="inlineStr"/>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>Year 6</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>Year 7</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CapEx</t>
-        </is>
-      </c>
-      <c r="C58" s="51">
-        <f>C53*C59</f>
-        <v/>
-      </c>
-      <c r="D58" s="51">
-        <f>D53*D59</f>
-        <v/>
-      </c>
-      <c r="E58" s="51">
-        <f>E53*E59</f>
-        <v/>
-      </c>
-      <c r="F58" s="51">
-        <f>F53*F59</f>
-        <v/>
-      </c>
-      <c r="G58" s="51">
-        <f>G53*G59</f>
+          <t>Revenue Growth</t>
+        </is>
+      </c>
+      <c r="C58" s="50">
+        <f>$B$35</f>
+        <v/>
+      </c>
+      <c r="D58" s="50">
+        <f>$B$36</f>
+        <v/>
+      </c>
+      <c r="E58" s="50">
+        <f>$B$37</f>
+        <v/>
+      </c>
+      <c r="F58" s="50">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="G58" s="50">
+        <f>$B$39</f>
+        <v/>
+      </c>
+      <c r="H58" s="50">
+        <f>$B$40</f>
+        <v/>
+      </c>
+      <c r="I58" s="50">
+        <f>$B$41</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CapEx %</t>
-        </is>
-      </c>
-      <c r="C59" s="47" t="n">
-        <v>0.0243</v>
-      </c>
-      <c r="D59" s="47" t="n">
-        <v>0.0228</v>
-      </c>
-      <c r="E59" s="47" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="F59" s="47" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="G59" s="47" t="n">
-        <v>0.0182</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B59" s="52" t="n">
+        <v>302969</v>
+      </c>
+      <c r="C59" s="52">
+        <f>B59*(1+C58)</f>
+        <v/>
+      </c>
+      <c r="D59" s="52">
+        <f>C59*(1+D58)</f>
+        <v/>
+      </c>
+      <c r="E59" s="52">
+        <f>D59*(1+E58)</f>
+        <v/>
+      </c>
+      <c r="F59" s="52">
+        <f>E59*(1+F58)</f>
+        <v/>
+      </c>
+      <c r="G59" s="52">
+        <f>F59*(1+G58)</f>
+        <v/>
+      </c>
+      <c r="H59" s="52">
+        <f>G59*(1+H58)</f>
+        <v/>
+      </c>
+      <c r="I59" s="52">
+        <f>H59*(1+I58)</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Change in NWC</t>
-        </is>
-      </c>
-      <c r="C60" s="51">
-        <f>$B$11*(C53-B53)</f>
-        <v/>
-      </c>
-      <c r="D60" s="51">
-        <f>$B$11*(D53-C53)</f>
-        <v/>
-      </c>
-      <c r="E60" s="51">
-        <f>$B$11*(E53-D53)</f>
-        <v/>
-      </c>
-      <c r="F60" s="51">
-        <f>$B$11*(F53-E53)</f>
-        <v/>
-      </c>
-      <c r="G60" s="51">
-        <f>$B$11*(G53-F53)</f>
-        <v/>
+          <t>Operating Margin</t>
+        </is>
+      </c>
+      <c r="B60" s="50" t="n">
+        <v>0.6521426284537362</v>
+      </c>
+      <c r="C60" s="47" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="D60" s="47" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="E60" s="47" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="F60" s="47" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="G60" s="47" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="H60" s="47" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="I60" s="47" t="n">
+        <v>0.6521</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Stock-Based Comp</t>
-        </is>
-      </c>
-      <c r="C61" s="51">
-        <f>C53*$B$12</f>
-        <v/>
-      </c>
-      <c r="D61" s="51">
-        <f>D53*$B$12</f>
-        <v/>
-      </c>
-      <c r="E61" s="51">
-        <f>E53*$B$12</f>
-        <v/>
-      </c>
-      <c r="F61" s="51">
-        <f>F53*$B$12</f>
-        <v/>
-      </c>
-      <c r="G61" s="51">
-        <f>G53*$B$12</f>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B61" s="52" t="n">
+        <v>197579</v>
+      </c>
+      <c r="C61" s="52">
+        <f>C59*C60</f>
+        <v/>
+      </c>
+      <c r="D61" s="52">
+        <f>D59*D60</f>
+        <v/>
+      </c>
+      <c r="E61" s="52">
+        <f>E59*E60</f>
+        <v/>
+      </c>
+      <c r="F61" s="52">
+        <f>F59*F60</f>
+        <v/>
+      </c>
+      <c r="G61" s="52">
+        <f>G59*G60</f>
+        <v/>
+      </c>
+      <c r="H61" s="52">
+        <f>H59*H60</f>
+        <v/>
+      </c>
+      <c r="I61" s="52">
+        <f>I59*I60</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Free Cash Flow</t>
-        </is>
-      </c>
-      <c r="C62" s="51">
-        <f>C56+C57-C58-C60-C61</f>
-        <v/>
-      </c>
-      <c r="D62" s="51">
-        <f>D56+D57-D58-D60-D61</f>
-        <v/>
-      </c>
-      <c r="E62" s="51">
-        <f>E56+E57-E58-E60-E61</f>
-        <v/>
-      </c>
-      <c r="F62" s="51">
-        <f>F56+F57-F58-F60-F61</f>
-        <v/>
-      </c>
-      <c r="G62" s="51">
-        <f>G56+G57-G58-G60-G61</f>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="C62" s="52">
+        <f>C61*(1-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D62" s="52">
+        <f>D61*(1-$B$6)</f>
+        <v/>
+      </c>
+      <c r="E62" s="52">
+        <f>E61*(1-$B$6)</f>
+        <v/>
+      </c>
+      <c r="F62" s="52">
+        <f>F61*(1-$B$6)</f>
+        <v/>
+      </c>
+      <c r="G62" s="52">
+        <f>G61*(1-$B$6)</f>
+        <v/>
+      </c>
+      <c r="H62" s="52">
+        <f>H61*(1-$B$6)</f>
+        <v/>
+      </c>
+      <c r="I62" s="52">
+        <f>I61*(1-$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FCF Margin</t>
-        </is>
-      </c>
-      <c r="C63" s="49">
-        <f>IF(C53&lt;&gt;0,C62/C53,0)</f>
-        <v/>
-      </c>
-      <c r="D63" s="49">
-        <f>IF(D53&lt;&gt;0,D62/D53,0)</f>
-        <v/>
-      </c>
-      <c r="E63" s="49">
-        <f>IF(E53&lt;&gt;0,E62/E53,0)</f>
-        <v/>
-      </c>
-      <c r="F63" s="49">
-        <f>IF(F53&lt;&gt;0,F62/F53,0)</f>
-        <v/>
-      </c>
-      <c r="G63" s="49">
-        <f>IF(G53&lt;&gt;0,G62/G53,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64"/>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C63" s="52">
+        <f>C59*$B$10</f>
+        <v/>
+      </c>
+      <c r="D63" s="52">
+        <f>D59*$B$10</f>
+        <v/>
+      </c>
+      <c r="E63" s="52">
+        <f>E59*$B$10</f>
+        <v/>
+      </c>
+      <c r="F63" s="52">
+        <f>F59*$B$10</f>
+        <v/>
+      </c>
+      <c r="G63" s="52">
+        <f>G59*$B$10</f>
+        <v/>
+      </c>
+      <c r="H63" s="52">
+        <f>H59*$B$10</f>
+        <v/>
+      </c>
+      <c r="I63" s="52">
+        <f>I59*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="C64" s="52">
+        <f>C59*C65</f>
+        <v/>
+      </c>
+      <c r="D64" s="52">
+        <f>D59*D65</f>
+        <v/>
+      </c>
+      <c r="E64" s="52">
+        <f>E59*E65</f>
+        <v/>
+      </c>
+      <c r="F64" s="52">
+        <f>F59*F65</f>
+        <v/>
+      </c>
+      <c r="G64" s="52">
+        <f>G59*G65</f>
+        <v/>
+      </c>
+      <c r="H64" s="52">
+        <f>H59*H65</f>
+        <v/>
+      </c>
+      <c r="I64" s="52">
+        <f>I59*I65</f>
+        <v/>
+      </c>
+    </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>DISCOUNTED CASH FLOWS ($M)</t>
-        </is>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CapEx %</t>
+        </is>
+      </c>
+      <c r="C65" s="47" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="D65" s="47" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="E65" s="47" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="F65" s="47" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="G65" s="47" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="H65" s="47" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="I65" s="47" t="n">
+        <v>0.0182</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PV of FCF</t>
-        </is>
-      </c>
-      <c r="C66" s="51">
-        <f>C62/(1+$B$4)^1</f>
-        <v/>
-      </c>
-      <c r="D66" s="51">
-        <f>D62/(1+$B$4)^2</f>
-        <v/>
-      </c>
-      <c r="E66" s="51">
-        <f>E62/(1+$B$4)^3</f>
-        <v/>
-      </c>
-      <c r="F66" s="51">
-        <f>F62/(1+$B$4)^4</f>
-        <v/>
-      </c>
-      <c r="G66" s="51">
-        <f>G62/(1+$B$4)^5</f>
+          <t>Change in NWC</t>
+        </is>
+      </c>
+      <c r="C66" s="52">
+        <f>$B$11*(C59-B59)</f>
+        <v/>
+      </c>
+      <c r="D66" s="52">
+        <f>$B$11*(D59-C59)</f>
+        <v/>
+      </c>
+      <c r="E66" s="52">
+        <f>$B$11*(E59-D59)</f>
+        <v/>
+      </c>
+      <c r="F66" s="52">
+        <f>$B$11*(F59-E59)</f>
+        <v/>
+      </c>
+      <c r="G66" s="52">
+        <f>$B$11*(G59-F59)</f>
+        <v/>
+      </c>
+      <c r="H66" s="52">
+        <f>$B$11*(H59-G59)</f>
+        <v/>
+      </c>
+      <c r="I66" s="52">
+        <f>$B$11*(I59-H59)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Terminal FCF (normalized)</t>
-        </is>
-      </c>
-      <c r="B67" s="51">
-        <f>G53*G54*(1-$B$6)+G53*$B$10-G53*$B$9-$B$11*G53*$B$5-G53*$B$12</f>
+          <t>Stock-Based Comp</t>
+        </is>
+      </c>
+      <c r="C67" s="52">
+        <f>C59*$B$12</f>
+        <v/>
+      </c>
+      <c r="D67" s="52">
+        <f>D59*$B$12</f>
+        <v/>
+      </c>
+      <c r="E67" s="52">
+        <f>E59*$B$12</f>
+        <v/>
+      </c>
+      <c r="F67" s="52">
+        <f>F59*$B$12</f>
+        <v/>
+      </c>
+      <c r="G67" s="52">
+        <f>G59*$B$12</f>
+        <v/>
+      </c>
+      <c r="H67" s="52">
+        <f>H59*$B$12</f>
+        <v/>
+      </c>
+      <c r="I67" s="52">
+        <f>I59*$B$12</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Terminal Value</t>
-        </is>
-      </c>
-      <c r="B68" s="51">
-        <f>B67*(1+$B$5)/($B$4-$B$5)</f>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="C68" s="52">
+        <f>C62+C63-C64-C66-C67</f>
+        <v/>
+      </c>
+      <c r="D68" s="52">
+        <f>D62+D63-D64-D66-D67</f>
+        <v/>
+      </c>
+      <c r="E68" s="52">
+        <f>E62+E63-E64-E66-E67</f>
+        <v/>
+      </c>
+      <c r="F68" s="52">
+        <f>F62+F63-F64-F66-F67</f>
+        <v/>
+      </c>
+      <c r="G68" s="52">
+        <f>G62+G63-G64-G66-G67</f>
+        <v/>
+      </c>
+      <c r="H68" s="52">
+        <f>H62+H63-H64-H66-H67</f>
+        <v/>
+      </c>
+      <c r="I68" s="52">
+        <f>I62+I63-I64-I66-I67</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PV of Terminal Value</t>
-        </is>
-      </c>
-      <c r="B69" s="51">
-        <f>B68/(1+$B$4)^5</f>
+          <t>FCF Margin</t>
+        </is>
+      </c>
+      <c r="C69" s="50">
+        <f>IF(C59&lt;&gt;0,C68/C59,0)</f>
+        <v/>
+      </c>
+      <c r="D69" s="50">
+        <f>IF(D59&lt;&gt;0,D68/D59,0)</f>
+        <v/>
+      </c>
+      <c r="E69" s="50">
+        <f>IF(E59&lt;&gt;0,E68/E59,0)</f>
+        <v/>
+      </c>
+      <c r="F69" s="50">
+        <f>IF(F59&lt;&gt;0,F68/F59,0)</f>
+        <v/>
+      </c>
+      <c r="G69" s="50">
+        <f>IF(G59&lt;&gt;0,G68/G59,0)</f>
+        <v/>
+      </c>
+      <c r="H69" s="50">
+        <f>IF(H59&lt;&gt;0,H68/H59,0)</f>
+        <v/>
+      </c>
+      <c r="I69" s="50">
+        <f>IF(I59&lt;&gt;0,I68/I59,0)</f>
         <v/>
       </c>
     </row>
@@ -5686,560 +5765,639 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>VALUATION SUMMARY</t>
+          <t>DISCOUNTED CASH FLOWS ($M)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sum of PV(FCFs)</t>
-        </is>
-      </c>
-      <c r="B72" s="51">
-        <f>SUM(C66:G66)</f>
+          <t>PV of FCF</t>
+        </is>
+      </c>
+      <c r="C72" s="52">
+        <f>C68*$B$15/(1+$B$4)^$B$14</f>
+        <v/>
+      </c>
+      <c r="D72" s="52">
+        <f>D68/(1+$B$4)^($B$14+1)</f>
+        <v/>
+      </c>
+      <c r="E72" s="52">
+        <f>E68/(1+$B$4)^($B$14+2)</f>
+        <v/>
+      </c>
+      <c r="F72" s="52">
+        <f>F68/(1+$B$4)^($B$14+3)</f>
+        <v/>
+      </c>
+      <c r="G72" s="52">
+        <f>G68/(1+$B$4)^($B$14+4)</f>
+        <v/>
+      </c>
+      <c r="H72" s="52">
+        <f>H68/(1+$B$4)^($B$14+5)</f>
+        <v/>
+      </c>
+      <c r="I72" s="52">
+        <f>I68/(1+$B$4)^($B$14+6)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PV of Terminal Value</t>
-        </is>
-      </c>
-      <c r="B73" s="51">
-        <f>B69</f>
+          <t>Terminal FCF (normalized)</t>
+        </is>
+      </c>
+      <c r="B73" s="52">
+        <f>I59*I60*(1-$B$6)+I59*$B$10-I59*$B$9-$B$11*I59*$B$5-I59*$B$12</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Value</t>
-        </is>
-      </c>
-      <c r="B74" s="51">
-        <f>B72+B73</f>
+          <t>Terminal Value</t>
+        </is>
+      </c>
+      <c r="B74" s="52">
+        <f>B73*(1+$B$5)/($B$4-$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Terminal Value % of EV</t>
+          <t>PV of Terminal Value</t>
         </is>
       </c>
       <c r="B75" s="52">
-        <f>IF(B74&lt;&gt;0,B73/B74,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Less: Debt</t>
-        </is>
-      </c>
-      <c r="B76" s="51">
-        <f>-B47</f>
-        <v/>
-      </c>
-    </row>
+        <f>B74/(1+$B$4)^($B$14+6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Plus: Cash</t>
-        </is>
-      </c>
-      <c r="B77" s="51">
-        <f>B46</f>
-        <v/>
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION SUMMARY</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Equity Value</t>
-        </is>
-      </c>
-      <c r="B78" s="51">
-        <f>B74+B76+B77</f>
+          <t>Sum of PV(FCFs)</t>
+        </is>
+      </c>
+      <c r="B78" s="52">
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Current Shares (M)</t>
-        </is>
-      </c>
-      <c r="B79" s="51">
-        <f>B48/1000000</f>
+          <t>PV of Terminal Value</t>
+        </is>
+      </c>
+      <c r="B79" s="52">
+        <f>B75</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Shares Used in Per-Share Calc (M)</t>
-        </is>
-      </c>
-      <c r="B80" s="51">
-        <f>B79</f>
+          <t>Enterprise Value</t>
+        </is>
+      </c>
+      <c r="B80" s="52">
+        <f>B78+B79</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Implied Share Price</t>
-        </is>
-      </c>
-      <c r="B81" s="135">
-        <f>IF(B80&lt;&gt;0,B78/B80,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82"/>
+          <t>Terminal Value % of EV</t>
+        </is>
+      </c>
+      <c r="B81" s="53">
+        <f>IF(B80&lt;&gt;0,B79/B80,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Less: Debt</t>
+        </is>
+      </c>
+      <c r="B82" s="52">
+        <f>-B53</f>
+        <v/>
+      </c>
+    </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>TERMINAL VALUE CROSS-CHECK</t>
-        </is>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Plus: Cash + Short-Term Investments</t>
+        </is>
+      </c>
+      <c r="B83" s="52">
+        <f>B51+B52</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Perpetuity Growth Method</t>
-        </is>
-      </c>
-      <c r="B84" s="51">
-        <f>B68</f>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="B84" s="52">
+        <f>B80+B82+B83</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Exit Multiple Method (25x EBITDA)</t>
-        </is>
-      </c>
-      <c r="B85" s="51" t="n">
-        <v>12836310</v>
+          <t>Current Shares (M)</t>
+        </is>
+      </c>
+      <c r="B85" s="52">
+        <f>B54/1000000</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="33" t="inlineStr">
-        <is>
-          <t>Note: Compare both methods. Large gaps suggest fragile assumptions.</t>
-        </is>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Shares Used in Per-Share Calc (M)</t>
+        </is>
+      </c>
+      <c r="B86" s="52">
+        <f>B85</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Current Market Price</t>
-        </is>
-      </c>
-      <c r="B87" s="136" t="n">
-        <v>230.36</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Upside / Downside</t>
-        </is>
-      </c>
-      <c r="B88" s="55">
-        <f>B81/B87-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89"/>
+          <t>Implied Share Price</t>
+        </is>
+      </c>
+      <c r="B87" s="133">
+        <f>IF(B86&lt;&gt;0,B84/B86,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>TERMINAL VALUE CROSS-CHECK</t>
+        </is>
+      </c>
+    </row>
     <row r="90">
-      <c r="A90" s="56" t="inlineStr">
-        <is>
-          <t>SCENARIO ANALYSIS</t>
-        </is>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Perpetuity Growth Method</t>
+        </is>
+      </c>
+      <c r="B90" s="52">
+        <f>B74</f>
+        <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="33" t="inlineStr">
-        <is>
-          <t>Scenarios driven by per-segment historical volatility (1-sigma bands)</t>
-        </is>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Implied Exit Multiple (TV / final-year EBITDA)</t>
+        </is>
+      </c>
+      <c r="B91" s="134" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="57" t="inlineStr">
-        <is>
-          <t>Bear - NVDA supply-bound: TSMC wafer/HBM bottleneck or 3-5yr ASIC erosion (demand confirmed 5/5 hyperscalers 2026)</t>
-        </is>
-      </c>
-      <c r="C92" s="58" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D92" s="59" t="inlineStr">
-        <is>
-          <t>Bull - NVDA supply execution: Blackwell yield gains, earlier Rubin ramp, hyperscalers raise 2026 capex again</t>
-        </is>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Peer EV/EBITDA today (median)</t>
+        </is>
+      </c>
+      <c r="B92" s="134" t="n">
+        <v>54.1</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>Implied Share Price</t>
-        </is>
-      </c>
-      <c r="B93" s="137" t="n">
-        <v>119.4137963644068</v>
-      </c>
-      <c r="C93" s="138" t="n">
-        <v>167.2033463366086</v>
-      </c>
-      <c r="D93" s="135" t="n">
-        <v>205.0729926535466</v>
+      <c r="A93" s="33" t="inlineStr">
+        <is>
+          <t>Note: this is the multiple the terminal value already implies, not a second valuation. Peers trade on growth still ahead of them, so a higher peer multiple is expected.</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>vs Current Price</t>
-        </is>
-      </c>
-      <c r="B94" s="139" t="n">
-        <v>-0.4816209569178383</v>
-      </c>
-      <c r="C94" s="140" t="n">
-        <v>-0.2741650185075162</v>
-      </c>
-      <c r="D94" s="141" t="n">
-        <v>-0.109771693638016</v>
+          <t>Current Market Price</t>
+        </is>
+      </c>
+      <c r="B94" s="135" t="n">
+        <v>221.3</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>Year 1 Growth</t>
-        </is>
-      </c>
-      <c r="B95" s="49" t="n">
-        <v>0.0409</v>
-      </c>
-      <c r="C95" s="49" t="n">
-        <v>0.3409</v>
-      </c>
-      <c r="D95" s="49" t="n">
-        <v>0.6409</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>Year 5 Growth</t>
-        </is>
-      </c>
-      <c r="B96" s="49" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="C96" s="49" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="D96" s="49" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Upside / Downside</t>
+        </is>
+      </c>
+      <c r="B95" s="57">
+        <f>B87/B94-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96"/>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Terminal Growth</t>
-        </is>
-      </c>
-      <c r="B97" s="49" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="C97" s="49" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="D97" s="49" t="n">
-        <v>0.035</v>
+      <c r="A97" s="58" t="inlineStr">
+        <is>
+          <t>SCENARIO ANALYSIS</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>Terminal Op Margin</t>
-        </is>
-      </c>
-      <c r="B98" s="65" t="n">
-        <v>0.58689</v>
-      </c>
-      <c r="C98" s="49" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="D98" s="49" t="n">
-        <v>0.6521</v>
+      <c r="A98" s="33" t="inlineStr">
+        <is>
+          <t>Bear and Bull are per-segment scenario bands; see the Scenarios tab for how each is derived</t>
+        </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="66" t="inlineStr">
-        <is>
-          <t>AI overlay (bear only; base/bull untouched): terminal margin cut 10%</t>
+      <c r="A99" s="1" t="inlineStr"/>
+      <c r="B99" s="59" t="inlineStr">
+        <is>
+          <t>Bear - Hyperscalers digest in CY28: FY28 lands on NVIDIA's ~70% call guide ($690.6B), then FY29 revenue is flat (the 2023 digestion pattern, after Goldman/UBS already see 2028 capex growth slowing to +12-17%), base rates after, and operating margin cuts to 58.7% from the stall year.</t>
+        </is>
+      </c>
+      <c r="C99" s="60" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D99" s="61" t="inlineStr">
+        <is>
+          <t>Bull - Customer demand is met: the CFO said customer forecasts point to growth doubling but supply limits it to ~70%; this bull lets supply catch up - FY28 revenue reaches 2x the base FY27, $812.5B - then grows at the base rates.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>Year 1 Op Margin</t>
-        </is>
-      </c>
-      <c r="B100" s="49" t="n">
-        <v>0.6071</v>
-      </c>
-      <c r="C100" s="49" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="D100" s="49" t="n">
-        <v>0.6821</v>
+          <t>Implied Share Price</t>
+        </is>
+      </c>
+      <c r="B100" s="136" t="n">
+        <v>172.1056419771127</v>
+      </c>
+      <c r="C100" s="137" t="n">
+        <v>230.0711683019033</v>
+      </c>
+      <c r="D100" s="133" t="n">
+        <v>270.4693593720563</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>Year 5 Op Margin</t>
-        </is>
-      </c>
-      <c r="B101" s="49" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="C101" s="49" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="D101" s="49" t="n">
-        <v>0.6521</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>vs Current Price</t>
+        </is>
+      </c>
+      <c r="B101" s="138" t="n">
+        <v>-0.2222971442516373</v>
+      </c>
+      <c r="C101" s="139" t="n">
+        <v>0.03963474153593881</v>
+      </c>
+      <c r="D101" s="140" t="n">
+        <v>0.2221841815275926</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>Net Dilution (SBC - Buybacks)</t>
-        </is>
-      </c>
-      <c r="B102" s="49" t="n">
-        <v>-0.008642512593634551</v>
-      </c>
-      <c r="C102" s="49" t="n">
-        <v>-0.008642512593634551</v>
-      </c>
-      <c r="D102" s="49" t="n">
-        <v>-0.008642512593634551</v>
-      </c>
-    </row>
-    <row r="103"/>
+          <t>Year 1 Growth</t>
+        </is>
+      </c>
+      <c r="B102" s="50" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="C102" s="50" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="D102" s="50" t="n">
+        <v>0.4001</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Year 7 Growth</t>
+        </is>
+      </c>
+      <c r="B103" s="50" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C103" s="50" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D103" s="50" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
     <row r="104">
-      <c r="A104" s="67" t="inlineStr">
-        <is>
-          <t>MARGIN REVERSION (stress case — base growth, mid-cycle margins)</t>
-        </is>
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Terminal Growth</t>
+        </is>
+      </c>
+      <c r="B104" s="50" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C104" s="50" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D104" s="50" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Stress Implied Share Price</t>
-        </is>
-      </c>
-      <c r="B105" s="142" t="n">
-        <v>131.4355471303862</v>
+          <t>Terminal Op Margin</t>
+        </is>
+      </c>
+      <c r="B105" s="50" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="C105" s="50" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="D105" s="50" t="n">
+        <v>0.6521</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>vs Base Case ($167.20)</t>
-        </is>
-      </c>
-      <c r="B106" s="143" t="n">
-        <v>-0.2139179627076109</v>
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Year 1 Op Margin</t>
+        </is>
+      </c>
+      <c r="B106" s="50" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="C106" s="50" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="D106" s="50" t="n">
+        <v>0.6581</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>vs Current Market ($230.36)</t>
-        </is>
-      </c>
-      <c r="B107" s="143" t="n">
-        <v>-0.4294341590103048</v>
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>Year 7 Op Margin</t>
+        </is>
+      </c>
+      <c r="B107" s="50" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="C107" s="50" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="D107" s="50" t="n">
+        <v>0.6521</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
+          <t>Net Dilution (SBC - Buybacks)</t>
+        </is>
+      </c>
+      <c r="B108" s="50" t="n">
+        <v>-0.008996336095516673</v>
+      </c>
+      <c r="C108" s="50" t="n">
+        <v>-0.008996336095516673</v>
+      </c>
+      <c r="D108" s="50" t="n">
+        <v>-0.008996336095516673</v>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="67" t="inlineStr">
+        <is>
+          <t>MARGIN REVERSION (stress case — base growth, mid-cycle margins)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>Stress Implied Share Price</t>
+        </is>
+      </c>
+      <c r="B111" s="141" t="n">
+        <v>182.9524690754535</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>vs Base Case ($230.07)</t>
+        </is>
+      </c>
+      <c r="B112" s="142" t="n">
+        <v>-0.2048005387820686</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>vs Current Market ($221.30)</t>
+        </is>
+      </c>
+      <c r="B113" s="142" t="n">
+        <v>-0.173283013667178</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
           <t>Year 1 → Year N Op Margin</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>65.2% → 50.0%</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="33" t="inlineStr">
-        <is>
-          <t>Holds driver-based revenue growth constant. Fades op margin linearly from TTM to − 5pp. Tests what happens if today's peak margins normalize to mid-cycle without any change in revenue trajectory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="56" t="inlineStr">
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="33" t="inlineStr">
+        <is>
+          <t>Holds driver-based revenue growth constant. Fades op margin linearly from TTM to the long-run margin target − 5pp. Tests what happens if today's peak margins normalize to mid-cycle without any change in revenue trajectory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="58" t="inlineStr">
         <is>
           <t>SENSITIVITY: WACC × Terminal Growth → Implied Price</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="33" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="33" t="inlineStr">
         <is>
           <t>Each cell shows the implied share price under that WACC / Terminal Growth combo</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="30" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="30" t="inlineStr">
         <is>
           <t>WACC ↓ / TGR →</t>
         </is>
       </c>
-      <c r="B114" s="70" t="n">
+      <c r="B120" s="70" t="n">
         <v>0.015</v>
       </c>
-      <c r="C114" s="70" t="n">
+      <c r="C120" s="70" t="n">
         <v>0.02</v>
       </c>
-      <c r="D114" s="70" t="n">
+      <c r="D120" s="70" t="n">
         <v>0.025</v>
       </c>
-      <c r="E114" s="70" t="n">
+      <c r="E120" s="70" t="n">
         <v>0.03</v>
       </c>
-      <c r="F114" s="70" t="n">
+      <c r="F120" s="70" t="n">
         <v>0.035</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="70" t="n">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="B115" s="136" t="n">
-        <v>181.4602707039947</v>
-      </c>
-      <c r="C115" s="136" t="n">
-        <v>190.9868047014702</v>
-      </c>
-      <c r="D115" s="136" t="n">
-        <v>201.8791788179705</v>
-      </c>
-      <c r="E115" s="136" t="n">
-        <v>214.4540484133934</v>
-      </c>
-      <c r="F115" s="136" t="n">
-        <v>229.1341510452569</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="70" t="n">
-        <v>0.1047</v>
-      </c>
-      <c r="B116" s="136" t="n">
-        <v>159.9746770336611</v>
-      </c>
-      <c r="C116" s="136" t="n">
-        <v>167.1652769376966</v>
-      </c>
-      <c r="D116" s="136" t="n">
-        <v>175.2572904127773</v>
-      </c>
-      <c r="E116" s="136" t="n">
-        <v>184.431724200077</v>
-      </c>
-      <c r="F116" s="136" t="n">
-        <v>194.9215238474188</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="70" t="n">
-        <v>0.1147</v>
-      </c>
-      <c r="B117" s="136" t="n">
-        <v>142.8315760838034</v>
-      </c>
-      <c r="C117" s="136" t="n">
-        <v>148.4069417960616</v>
-      </c>
-      <c r="D117" s="136" t="n">
-        <v>154.6031894501711</v>
-      </c>
-      <c r="E117" s="136" t="n">
-        <v>161.5302745257989</v>
-      </c>
-      <c r="F117" s="144" t="n">
-        <v>169.3257448438078</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="70" t="n">
-        <v>0.1247</v>
-      </c>
-      <c r="B118" s="136" t="n">
-        <v>128.8422093361122</v>
-      </c>
-      <c r="C118" s="136" t="n">
-        <v>133.2598496106757</v>
-      </c>
-      <c r="D118" s="136" t="n">
-        <v>138.1200024234396</v>
-      </c>
-      <c r="E118" s="136" t="n">
-        <v>143.4927595175189</v>
-      </c>
-      <c r="F118" s="136" t="n">
-        <v>149.4638406723979</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="70" t="n">
-        <v>0.1347</v>
-      </c>
-      <c r="B119" s="136" t="n">
-        <v>117.2151203392598</v>
-      </c>
-      <c r="C119" s="136" t="n">
-        <v>120.7784517931746</v>
-      </c>
-      <c r="D119" s="136" t="n">
-        <v>124.6661033813538</v>
-      </c>
-      <c r="E119" s="136" t="n">
-        <v>128.9245393064141</v>
-      </c>
-      <c r="F119" s="136" t="n">
-        <v>133.6095445739043</v>
+    <row r="121">
+      <c r="A121" s="70" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="B121" s="135" t="n">
+        <v>254.1911479939686</v>
+      </c>
+      <c r="C121" s="135" t="n">
+        <v>265.4182387704171</v>
+      </c>
+      <c r="D121" s="135" t="n">
+        <v>278.1675107590254</v>
+      </c>
+      <c r="E121" s="135" t="n">
+        <v>292.7713179362481</v>
+      </c>
+      <c r="F121" s="135" t="n">
+        <v>309.6663640356676</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="70" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="B122" s="135" t="n">
+        <v>225.5597274698337</v>
+      </c>
+      <c r="C122" s="135" t="n">
+        <v>234.0318719963358</v>
+      </c>
+      <c r="D122" s="135" t="n">
+        <v>243.5152479400777</v>
+      </c>
+      <c r="E122" s="135" t="n">
+        <v>254.2025931823631</v>
+      </c>
+      <c r="F122" s="135" t="n">
+        <v>266.3389489644151</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="70" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="B123" s="135" t="n">
+        <v>202.5062872882993</v>
+      </c>
+      <c r="C123" s="135" t="n">
+        <v>209.0593580701734</v>
+      </c>
+      <c r="D123" s="135" t="n">
+        <v>216.3109753273014</v>
+      </c>
+      <c r="E123" s="135" t="n">
+        <v>224.3792698052166</v>
+      </c>
+      <c r="F123" s="143" t="n">
+        <v>233.4105994287913</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="70" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="B124" s="135" t="n">
+        <v>183.5566716323445</v>
+      </c>
+      <c r="C124" s="135" t="n">
+        <v>188.7282902557457</v>
+      </c>
+      <c r="D124" s="135" t="n">
+        <v>194.3979173006549</v>
+      </c>
+      <c r="E124" s="135" t="n">
+        <v>200.6412379375141</v>
+      </c>
+      <c r="F124" s="135" t="n">
+        <v>207.5500921223452</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="70" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="B125" s="135" t="n">
+        <v>167.7135399022762</v>
+      </c>
+      <c r="C125" s="135" t="n">
+        <v>171.8636527664494</v>
+      </c>
+      <c r="D125" s="135" t="n">
+        <v>176.3781661899029</v>
+      </c>
+      <c r="E125" s="135" t="n">
+        <v>181.3073654384068</v>
+      </c>
+      <c r="F125" s="135" t="n">
+        <v>186.7112339967803</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A109:D109"/>
-    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A110:D110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6293,7 +6451,7 @@
         </is>
       </c>
       <c r="B5" s="73" t="n">
-        <v>0.2998779296875</v>
+        <v>0.22587890625</v>
       </c>
     </row>
     <row r="6">
@@ -6302,8 +6460,8 @@
           <t>Current Stock Price</t>
         </is>
       </c>
-      <c r="B6" s="136" t="n">
-        <v>230.36</v>
+      <c r="B6" s="135" t="n">
+        <v>221.3</v>
       </c>
     </row>
     <row r="7"/>
@@ -6347,15 +6505,15 @@
     <row r="12">
       <c r="A12" s="75" t="inlineStr">
         <is>
-          <t>✓ Market implies 30% growth vs 110% historical — conservative pricing</t>
+          <t>✓ Market implies 23% growth vs 110% historical — conservative pricing</t>
         </is>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="160" t="inlineStr">
-        <is>
-          <t>The market expects strong growth (30%/yr). Reasonable for high-growth tech but watch for deceleration.</t>
+      <c r="A14" s="76" t="inlineStr">
+        <is>
+          <t>The market expects strong growth (23%/yr). Reasonable for high-growth tech but watch for deceleration.</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6521,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>WHAT MUST BE TRUE FOR $230 TO BE FAIR VALUE</t>
+          <t>WHAT MUST BE TRUE FOR $221 TO BE FAIR VALUE</t>
         </is>
       </c>
     </row>
@@ -6381,11 +6539,11 @@
         </is>
       </c>
       <c r="B18" s="77" t="n">
-        <v>411767.1206298828</v>
+        <v>299130.110571289</v>
       </c>
       <c r="C18" s="78" t="inlineStr">
         <is>
-          <t>vs base $302,969M (Δ +36%)</t>
+          <t>vs base $302,969M (Δ -1%)</t>
         </is>
       </c>
     </row>
@@ -6395,9 +6553,12 @@
           <t>Required Operating Margin (held constant)</t>
         </is>
       </c>
-      <c r="B19" s="78" t="inlineStr">
-        <is>
-          <t>out of search range</t>
+      <c r="B19" s="79" t="n">
+        <v>0.6455078125</v>
+      </c>
+      <c r="C19" s="78" t="inlineStr">
+        <is>
+          <t>vs base 65.2% (Δ -0.7pp) → implied FCF margin 50.6%</t>
         </is>
       </c>
     </row>
@@ -6408,11 +6569,11 @@
         </is>
       </c>
       <c r="B20" s="79" t="n">
-        <v>0.06020890173484607</v>
+        <v>0.0336624718390257</v>
       </c>
       <c r="C20" s="78" t="inlineStr">
         <is>
-          <t>vs base 3.5% (Δ +2.5pp)</t>
+          <t>vs base 3.5% (Δ -0.1pp)</t>
         </is>
       </c>
     </row>
@@ -6540,184 +6701,184 @@
     </row>
     <row r="33">
       <c r="A33" s="82" t="n">
-        <v>0.0847</v>
-      </c>
-      <c r="B33" s="49" t="n">
-        <v>0.255615234375</v>
-      </c>
-      <c r="C33" s="49" t="n">
-        <v>0.239892578125</v>
-      </c>
-      <c r="D33" s="49" t="n">
-        <v>0.22314453125</v>
-      </c>
-      <c r="E33" s="49" t="n">
-        <v>0.20537109375</v>
-      </c>
-      <c r="F33" s="49" t="n">
-        <v>0.1860595703125</v>
-      </c>
-      <c r="G33" s="49" t="n">
-        <v>0.1652099609375</v>
-      </c>
-      <c r="H33" s="49" t="n">
-        <v>0.14248046875</v>
+        <v>0.0887</v>
+      </c>
+      <c r="B33" s="50" t="n">
+        <v>0.1884521484375</v>
+      </c>
+      <c r="C33" s="50" t="n">
+        <v>0.179052734375</v>
+      </c>
+      <c r="D33" s="50" t="n">
+        <v>0.168798828125</v>
+      </c>
+      <c r="E33" s="50" t="n">
+        <v>0.1580322265625</v>
+      </c>
+      <c r="F33" s="50" t="n">
+        <v>0.146240234375</v>
+      </c>
+      <c r="G33" s="50" t="n">
+        <v>0.1334228515625</v>
+      </c>
+      <c r="H33" s="50" t="n">
+        <v>0.119580078125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="82" t="n">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <v>0.294580078125</v>
-      </c>
-      <c r="C34" s="49" t="n">
-        <v>0.2803955078125</v>
-      </c>
-      <c r="D34" s="49" t="n">
-        <v>0.26552734375</v>
-      </c>
-      <c r="E34" s="49" t="n">
-        <v>0.2496337890625</v>
-      </c>
-      <c r="F34" s="49" t="n">
-        <v>0.23271484375</v>
-      </c>
-      <c r="G34" s="49" t="n">
-        <v>0.214599609375</v>
-      </c>
-      <c r="H34" s="49" t="n">
-        <v>0.1952880859375</v>
+        <v>0.0987</v>
+      </c>
+      <c r="B34" s="50" t="n">
+        <v>0.2154541015625</v>
+      </c>
+      <c r="C34" s="50" t="n">
+        <v>0.2069091796875</v>
+      </c>
+      <c r="D34" s="50" t="n">
+        <v>0.1980224609375</v>
+      </c>
+      <c r="E34" s="50" t="n">
+        <v>0.1884521484375</v>
+      </c>
+      <c r="F34" s="50" t="n">
+        <v>0.1781982421875</v>
+      </c>
+      <c r="G34" s="50" t="n">
+        <v>0.16708984375</v>
+      </c>
+      <c r="H34" s="50" t="n">
+        <v>0.1552978515625</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="82" t="n">
-        <v>0.1047</v>
-      </c>
-      <c r="B35" s="49" t="n">
-        <v>0.330810546875</v>
-      </c>
-      <c r="C35" s="49" t="n">
-        <v>0.3179931640625001</v>
-      </c>
-      <c r="D35" s="49" t="n">
-        <v>0.3044921875</v>
-      </c>
-      <c r="E35" s="49" t="n">
-        <v>0.29013671875</v>
-      </c>
-      <c r="F35" s="49" t="n">
-        <v>0.27509765625</v>
-      </c>
-      <c r="G35" s="49" t="n">
-        <v>0.2592041015625</v>
-      </c>
-      <c r="H35" s="49" t="n">
-        <v>0.24228515625</v>
+        <v>0.1087</v>
+      </c>
+      <c r="B35" s="50" t="n">
+        <v>0.2407470703125</v>
+      </c>
+      <c r="C35" s="50" t="n">
+        <v>0.233056640625</v>
+      </c>
+      <c r="D35" s="50" t="n">
+        <v>0.2250244140625</v>
+      </c>
+      <c r="E35" s="50" t="n">
+        <v>0.2164794921875</v>
+      </c>
+      <c r="F35" s="50" t="n">
+        <v>0.207421875</v>
+      </c>
+      <c r="G35" s="50" t="n">
+        <v>0.1976806640625</v>
+      </c>
+      <c r="H35" s="50" t="n">
+        <v>0.1874267578125</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="82" t="n">
-        <v>0.1147</v>
-      </c>
-      <c r="B36" s="49" t="n">
-        <v>0.36533203125</v>
-      </c>
-      <c r="C36" s="49" t="n">
-        <v>0.353369140625</v>
-      </c>
-      <c r="D36" s="49" t="n">
-        <v>0.341064453125</v>
-      </c>
-      <c r="E36" s="49" t="n">
-        <v>0.328076171875</v>
-      </c>
-      <c r="F36" s="49" t="n">
-        <v>0.314404296875</v>
-      </c>
-      <c r="G36" s="55" t="n">
-        <v>0.300048828125</v>
-      </c>
-      <c r="H36" s="49" t="n">
-        <v>0.285009765625</v>
+        <v>0.1187</v>
+      </c>
+      <c r="B36" s="50" t="n">
+        <v>0.26484375</v>
+      </c>
+      <c r="C36" s="50" t="n">
+        <v>0.2578369140625</v>
+      </c>
+      <c r="D36" s="50" t="n">
+        <v>0.25048828125</v>
+      </c>
+      <c r="E36" s="50" t="n">
+        <v>0.2427978515625</v>
+      </c>
+      <c r="F36" s="50" t="n">
+        <v>0.2345947265625</v>
+      </c>
+      <c r="G36" s="57" t="n">
+        <v>0.22587890625</v>
+      </c>
+      <c r="H36" s="50" t="n">
+        <v>0.2168212890625</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="82" t="n">
-        <v>0.1247</v>
-      </c>
-      <c r="B37" s="49" t="n">
-        <v>0.3979736328125</v>
-      </c>
-      <c r="C37" s="49" t="n">
-        <v>0.3870361328125</v>
-      </c>
-      <c r="D37" s="49" t="n">
-        <v>0.3755859375</v>
-      </c>
-      <c r="E37" s="49" t="n">
-        <v>0.363623046875</v>
-      </c>
-      <c r="F37" s="49" t="n">
-        <v>0.3513183593750001</v>
-      </c>
-      <c r="G37" s="49" t="n">
-        <v>0.3381591796875</v>
-      </c>
-      <c r="H37" s="49" t="n">
-        <v>0.3244873046875</v>
+        <v>0.1287</v>
+      </c>
+      <c r="B37" s="50" t="n">
+        <v>0.2879150390625</v>
+      </c>
+      <c r="C37" s="50" t="n">
+        <v>0.2814208984375</v>
+      </c>
+      <c r="D37" s="50" t="n">
+        <v>0.274755859375</v>
+      </c>
+      <c r="E37" s="50" t="n">
+        <v>0.267578125</v>
+      </c>
+      <c r="F37" s="50" t="n">
+        <v>0.2602294921875</v>
+      </c>
+      <c r="G37" s="50" t="n">
+        <v>0.2523681640625</v>
+      </c>
+      <c r="H37" s="50" t="n">
+        <v>0.2441650390625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="82" t="n">
-        <v>0.1347</v>
-      </c>
-      <c r="B38" s="83" t="n">
-        <v>0.4294189453124999</v>
-      </c>
-      <c r="C38" s="83" t="n">
-        <v>0.4191650390625</v>
-      </c>
-      <c r="D38" s="83" t="n">
-        <v>0.4085693359374999</v>
-      </c>
-      <c r="E38" s="49" t="n">
-        <v>0.3974609375</v>
-      </c>
-      <c r="F38" s="49" t="n">
-        <v>0.3860107421875</v>
-      </c>
-      <c r="G38" s="49" t="n">
-        <v>0.373876953125</v>
-      </c>
-      <c r="H38" s="49" t="n">
-        <v>0.3614013671875</v>
+        <v>0.1387</v>
+      </c>
+      <c r="B38" s="50" t="n">
+        <v>0.3099609375</v>
+      </c>
+      <c r="C38" s="50" t="n">
+        <v>0.3039794921875</v>
+      </c>
+      <c r="D38" s="50" t="n">
+        <v>0.2978271484375</v>
+      </c>
+      <c r="E38" s="50" t="n">
+        <v>0.2913330078125</v>
+      </c>
+      <c r="F38" s="50" t="n">
+        <v>0.2844970703125</v>
+      </c>
+      <c r="G38" s="50" t="n">
+        <v>0.2773193359375</v>
+      </c>
+      <c r="H38" s="50" t="n">
+        <v>0.2697998046875</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="82" t="n">
-        <v>0.1447</v>
-      </c>
-      <c r="B39" s="83" t="n">
-        <v>0.45966796875</v>
-      </c>
-      <c r="C39" s="83" t="n">
-        <v>0.45009765625</v>
-      </c>
-      <c r="D39" s="83" t="n">
-        <v>0.440185546875</v>
-      </c>
-      <c r="E39" s="83" t="n">
-        <v>0.4299316406249999</v>
-      </c>
-      <c r="F39" s="83" t="n">
-        <v>0.418994140625</v>
-      </c>
-      <c r="G39" s="83" t="n">
-        <v>0.4080566406249999</v>
-      </c>
-      <c r="H39" s="49" t="n">
-        <v>0.396435546875</v>
+        <v>0.1487</v>
+      </c>
+      <c r="B39" s="50" t="n">
+        <v>0.3314941406249999</v>
+      </c>
+      <c r="C39" s="50" t="n">
+        <v>0.3258544921875</v>
+      </c>
+      <c r="D39" s="50" t="n">
+        <v>0.3200439453125</v>
+      </c>
+      <c r="E39" s="50" t="n">
+        <v>0.3140625</v>
+      </c>
+      <c r="F39" s="50" t="n">
+        <v>0.3077392578125</v>
+      </c>
+      <c r="G39" s="50" t="n">
+        <v>0.30107421875</v>
+      </c>
+      <c r="H39" s="50" t="n">
+        <v>0.29423828125</v>
       </c>
     </row>
     <row r="40"/>
@@ -6743,126 +6904,126 @@
         </is>
       </c>
       <c r="B44" s="82" t="n">
-        <v>0.1998779296875</v>
+        <v>0.12587890625</v>
       </c>
       <c r="C44" s="82" t="n">
-        <v>0.2498779296875</v>
+        <v>0.17587890625</v>
       </c>
       <c r="D44" s="82" t="n">
-        <v>0.2998779296875</v>
+        <v>0.22587890625</v>
       </c>
       <c r="E44" s="82" t="n">
-        <v>0.3498779296875</v>
+        <v>0.27587890625</v>
       </c>
       <c r="F44" s="82" t="n">
-        <v>0.3998779296875</v>
+        <v>0.32587890625</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="82" t="n">
         <v>0.5521426284537362</v>
       </c>
-      <c r="B45" s="136" t="n">
-        <v>133.2085207966008</v>
-      </c>
-      <c r="C45" s="136" t="n">
-        <v>160.4306837462852</v>
-      </c>
-      <c r="D45" s="136" t="n">
-        <v>192.1313590074631</v>
-      </c>
-      <c r="E45" s="136" t="n">
-        <v>228.8539496904029</v>
-      </c>
-      <c r="F45" s="136" t="n">
-        <v>271.184544946347</v>
+      <c r="B45" s="135" t="n">
+        <v>110.7358334654612</v>
+      </c>
+      <c r="C45" s="135" t="n">
+        <v>143.3294381218944</v>
+      </c>
+      <c r="D45" s="135" t="n">
+        <v>184.651566992911</v>
+      </c>
+      <c r="E45" s="135" t="n">
+        <v>236.6375673555049</v>
+      </c>
+      <c r="F45" s="135" t="n">
+        <v>301.5567601428133</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="82" t="n">
         <v>0.6021426284537361</v>
       </c>
-      <c r="B46" s="136" t="n">
-        <v>146.3282445058916</v>
-      </c>
-      <c r="C46" s="136" t="n">
-        <v>176.2341938233468</v>
-      </c>
-      <c r="D46" s="136" t="n">
-        <v>211.059900115512</v>
-      </c>
-      <c r="E46" s="136" t="n">
-        <v>251.4022860853929</v>
-      </c>
-      <c r="F46" s="136" t="n">
-        <v>297.9051636545441</v>
+      <c r="B46" s="135" t="n">
+        <v>121.5189028180583</v>
+      </c>
+      <c r="C46" s="135" t="n">
+        <v>157.3303610364251</v>
+      </c>
+      <c r="D46" s="135" t="n">
+        <v>202.7312859808081</v>
+      </c>
+      <c r="E46" s="135" t="n">
+        <v>259.8478225622137</v>
+      </c>
+      <c r="F46" s="135" t="n">
+        <v>331.1730039373285</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="82" t="n">
         <v>0.6521426284537362</v>
       </c>
-      <c r="B47" s="136" t="n">
-        <v>159.4479682151824</v>
-      </c>
-      <c r="C47" s="136" t="n">
-        <v>192.0377039004085</v>
-      </c>
-      <c r="D47" s="144" t="n">
-        <v>229.9884412235609</v>
-      </c>
-      <c r="E47" s="136" t="n">
-        <v>273.9506224803828</v>
-      </c>
-      <c r="F47" s="136" t="n">
-        <v>324.6257823627412</v>
+      <c r="B47" s="135" t="n">
+        <v>132.3019721706555</v>
+      </c>
+      <c r="C47" s="135" t="n">
+        <v>171.3312839509559</v>
+      </c>
+      <c r="D47" s="143" t="n">
+        <v>220.8110049687053</v>
+      </c>
+      <c r="E47" s="135" t="n">
+        <v>283.0580777689226</v>
+      </c>
+      <c r="F47" s="135" t="n">
+        <v>360.7892477318436</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="82" t="n">
         <v>0.7021426284537362</v>
       </c>
-      <c r="B48" s="136" t="n">
-        <v>172.5676919244732</v>
-      </c>
-      <c r="C48" s="136" t="n">
-        <v>207.8412139774702</v>
-      </c>
-      <c r="D48" s="136" t="n">
-        <v>248.9169823316097</v>
-      </c>
-      <c r="E48" s="136" t="n">
-        <v>296.4989588753729</v>
-      </c>
-      <c r="F48" s="136" t="n">
-        <v>351.3464010709383</v>
+      <c r="B48" s="135" t="n">
+        <v>143.0850415232526</v>
+      </c>
+      <c r="C48" s="135" t="n">
+        <v>185.3322068654865</v>
+      </c>
+      <c r="D48" s="135" t="n">
+        <v>238.8907239566024</v>
+      </c>
+      <c r="E48" s="135" t="n">
+        <v>306.2683329756315</v>
+      </c>
+      <c r="F48" s="135" t="n">
+        <v>390.4054915263588</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="82" t="n">
         <v>0.7521426284537361</v>
       </c>
-      <c r="B49" s="136" t="n">
-        <v>185.6874156337639</v>
-      </c>
-      <c r="C49" s="136" t="n">
-        <v>223.6447240545319</v>
-      </c>
-      <c r="D49" s="136" t="n">
-        <v>267.8455234396587</v>
-      </c>
-      <c r="E49" s="136" t="n">
-        <v>319.0472952703628</v>
-      </c>
-      <c r="F49" s="136" t="n">
-        <v>378.0670197791355</v>
+      <c r="B49" s="135" t="n">
+        <v>153.8681108758497</v>
+      </c>
+      <c r="C49" s="135" t="n">
+        <v>199.3331297800172</v>
+      </c>
+      <c r="D49" s="135" t="n">
+        <v>256.9704429444996</v>
+      </c>
+      <c r="E49" s="135" t="n">
+        <v>329.4785881823403</v>
+      </c>
+      <c r="F49" s="135" t="n">
+        <v>420.021735320874</v>
       </c>
     </row>
     <row r="50"/>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="84" t="inlineStr">
-        <is>
-          <t>At current price $230.36, the market is pricing in approximately 30% revenue CAGR AT 65% operating margin. Move along either axis to see the trade-off.</t>
+      <c r="A51" s="83" t="inlineStr">
+        <is>
+          <t>At current price $221.30, the market is pricing in approximately 23% revenue CAGR AT 65% operating margin. Move along either axis to see the trade-off.</t>
         </is>
       </c>
     </row>
@@ -6889,7 +7050,7 @@
         </is>
       </c>
       <c r="B56" s="47" t="n">
-        <v>0.1146510108547472</v>
+        <v>0.1186991999103706</v>
       </c>
     </row>
     <row r="57">
@@ -6898,8 +7059,8 @@
           <t>Market-Implied WACC</t>
         </is>
       </c>
-      <c r="B57" s="55" t="n">
-        <v>0.09439697265625001</v>
+      <c r="B57" s="57" t="n">
+        <v>0.11972412109375</v>
       </c>
     </row>
     <row r="58">
@@ -6908,14 +7069,14 @@
           <t>Gap (Ours − Market)</t>
         </is>
       </c>
-      <c r="B58" s="161" t="n">
-        <v>0.02025403819849723</v>
+      <c r="B58" s="144" t="n">
+        <v>-0.001024921183379421</v>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="84" t="inlineStr">
-        <is>
-          <t>We discount at 2.0pp HIGHER than the market. Closing this gap (lower beta or longer return horizon) would push our DCF toward sell-side targets.</t>
+      <c r="A59" s="83" t="inlineStr">
+        <is>
+          <t>Our discount rate is in line with the market's implied cost of capital.</t>
         </is>
       </c>
     </row>
@@ -6978,7 +7139,7 @@
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
         <is>
-          <t>WACC: Normal(11.5%, 1.5% std) | TGR: Triangular(2.0%, 3.5%, 5.0%)</t>
+          <t>WACC: Normal(11.9%, 1.5% std) | TGR: Triangular(2.0%, 3.5%, 5.0%)</t>
         </is>
       </c>
     </row>
@@ -7012,8 +7173,8 @@
           <t>Mean Implied Price</t>
         </is>
       </c>
-      <c r="B11" s="146" t="n">
-        <v>177.5009717583784</v>
+      <c r="B11" s="145" t="n">
+        <v>240.2135320766943</v>
       </c>
     </row>
     <row r="12">
@@ -7022,8 +7183,8 @@
           <t>Median Implied Price (50th pctl)</t>
         </is>
       </c>
-      <c r="B12" s="146" t="n">
-        <v>167.8871316945239</v>
+      <c r="B12" s="145" t="n">
+        <v>228.2890193163419</v>
       </c>
     </row>
     <row r="13">
@@ -7032,8 +7193,8 @@
           <t>Standard Deviation</t>
         </is>
       </c>
-      <c r="B13" s="146" t="n">
-        <v>51.84161939992322</v>
+      <c r="B13" s="145" t="n">
+        <v>69.905571361395</v>
       </c>
     </row>
     <row r="14"/>
@@ -7047,17 +7208,17 @@
       <c r="C15" s="45" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="87" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>Percentile</t>
         </is>
       </c>
-      <c r="B16" s="87" t="inlineStr">
+      <c r="B16" s="86" t="inlineStr">
         <is>
           <t>Implied Price</t>
         </is>
       </c>
-      <c r="C16" s="87" t="inlineStr">
+      <c r="C16" s="86" t="inlineStr">
         <is>
           <t>vs Current</t>
         </is>
@@ -7069,11 +7230,11 @@
           <t>5th</t>
         </is>
       </c>
-      <c r="B17" s="136" t="n">
-        <v>111.6447341225524</v>
-      </c>
-      <c r="C17" s="147" t="n">
-        <v>-0.5153467002841102</v>
+      <c r="B17" s="135" t="n">
+        <v>149.3653136936264</v>
+      </c>
+      <c r="C17" s="146" t="n">
+        <v>-0.3250550669063427</v>
       </c>
     </row>
     <row r="18">
@@ -7082,11 +7243,11 @@
           <t>25th</t>
         </is>
       </c>
-      <c r="B18" s="136" t="n">
-        <v>142.8236904796395</v>
-      </c>
-      <c r="C18" s="147" t="n">
-        <v>-0.3799978708124695</v>
+      <c r="B18" s="135" t="n">
+        <v>194.0969537990135</v>
+      </c>
+      <c r="C18" s="146" t="n">
+        <v>-0.1229238418481088</v>
       </c>
     </row>
     <row r="19">
@@ -7095,11 +7256,11 @@
           <t>50th</t>
         </is>
       </c>
-      <c r="B19" s="148" t="n">
-        <v>167.8871316945239</v>
-      </c>
-      <c r="C19" s="147" t="n">
-        <v>-0.2711966847780695</v>
+      <c r="B19" s="147" t="n">
+        <v>228.2890193163419</v>
+      </c>
+      <c r="C19" s="148" t="n">
+        <v>0.0315816507742519</v>
       </c>
     </row>
     <row r="20">
@@ -7108,11 +7269,11 @@
           <t>75th</t>
         </is>
       </c>
-      <c r="B20" s="136" t="n">
-        <v>200.2782522083899</v>
-      </c>
-      <c r="C20" s="147" t="n">
-        <v>-0.1305858126046625</v>
+      <c r="B20" s="135" t="n">
+        <v>274.961899973094</v>
+      </c>
+      <c r="C20" s="148" t="n">
+        <v>0.242484862056457</v>
       </c>
     </row>
     <row r="21">
@@ -7121,11 +7282,11 @@
           <t>95th</t>
         </is>
       </c>
-      <c r="B21" s="136" t="n">
-        <v>272.8729606841532</v>
-      </c>
-      <c r="C21" s="149" t="n">
-        <v>0.1845500984726218</v>
+      <c r="B21" s="135" t="n">
+        <v>371.0765033091839</v>
+      </c>
+      <c r="C21" s="148" t="n">
+        <v>0.6768029973302481</v>
       </c>
     </row>
     <row r="22"/>
@@ -7144,8 +7305,8 @@
           <t>Current Share Price</t>
         </is>
       </c>
-      <c r="B24" s="136" t="n">
-        <v>230.36</v>
+      <c r="B24" s="135" t="n">
+        <v>221.3</v>
       </c>
     </row>
     <row r="25">
@@ -7154,12 +7315,12 @@
           <t>P(Undervalued)</t>
         </is>
       </c>
-      <c r="B25" s="91" t="n">
-        <v>0.135</v>
+      <c r="B25" s="90" t="n">
+        <v>0.542</v>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
-          <t>Majority of scenarios imply downside</t>
+          <t>Majority of scenarios imply upside</t>
         </is>
       </c>
     </row>
@@ -7179,8 +7340,8 @@
           <t>Bear Implied</t>
         </is>
       </c>
-      <c r="B28" s="150" t="n">
-        <v>119.4137963644068</v>
+      <c r="B28" s="149" t="n">
+        <v>172.1056419771127</v>
       </c>
     </row>
     <row r="29">
@@ -7189,8 +7350,8 @@
           <t>Base Implied</t>
         </is>
       </c>
-      <c r="B29" s="151" t="n">
-        <v>167.2033463366086</v>
+      <c r="B29" s="150" t="n">
+        <v>230.0711683019033</v>
       </c>
     </row>
     <row r="30">
@@ -7199,8 +7360,8 @@
           <t>Bull Implied</t>
         </is>
       </c>
-      <c r="B30" s="144" t="n">
-        <v>205.0729926535466</v>
+      <c r="B30" s="143" t="n">
+        <v>270.4693593720563</v>
       </c>
     </row>
     <row r="31"/>
@@ -7214,302 +7375,314 @@
       <c r="C32" s="45" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="94" t="inlineStr">
-        <is>
-          <t>$79-$102</t>
-        </is>
-      </c>
-      <c r="B33" s="95" t="inlineStr">
+      <c r="A33" s="93" t="inlineStr">
+        <is>
+          <t>$103-$130</t>
+        </is>
+      </c>
+      <c r="B33" s="94" t="inlineStr">
         <is>
           <t>███</t>
         </is>
       </c>
-      <c r="C33" s="96" t="inlineStr">
-        <is>
-          <t>(22)</t>
+      <c r="C33" s="95" t="inlineStr">
+        <is>
+          <t>(15)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="inlineStr">
-        <is>
-          <t>$102-$125</t>
-        </is>
-      </c>
-      <c r="B34" s="95" t="inlineStr">
-        <is>
-          <t>████████████████</t>
-        </is>
-      </c>
-      <c r="C34" s="96" t="inlineStr">
-        <is>
-          <t>(98)</t>
+      <c r="A34" s="93" t="inlineStr">
+        <is>
+          <t>$130-$157</t>
+        </is>
+      </c>
+      <c r="B34" s="94" t="inlineStr">
+        <is>
+          <t>█████████████</t>
+        </is>
+      </c>
+      <c r="C34" s="95" t="inlineStr">
+        <is>
+          <t>(64)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="94" t="inlineStr">
-        <is>
-          <t>$125-$149</t>
-        </is>
-      </c>
-      <c r="B35" s="95" t="inlineStr">
-        <is>
-          <t>██████████████████████████████</t>
-        </is>
-      </c>
-      <c r="C35" s="96" t="inlineStr">
-        <is>
-          <t>(184)</t>
+      <c r="A35" s="93" t="inlineStr">
+        <is>
+          <t>$157-$184</t>
+        </is>
+      </c>
+      <c r="B35" s="94" t="inlineStr">
+        <is>
+          <t>███████████████████████</t>
+        </is>
+      </c>
+      <c r="C35" s="95" t="inlineStr">
+        <is>
+          <t>(110)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="94" t="inlineStr">
-        <is>
-          <t>$149-$172</t>
-        </is>
-      </c>
-      <c r="B36" s="95" t="inlineStr">
+      <c r="A36" s="93" t="inlineStr">
+        <is>
+          <t>$184-$210</t>
+        </is>
+      </c>
+      <c r="B36" s="94" t="inlineStr">
         <is>
           <t>████████████████████████████████████████</t>
         </is>
       </c>
-      <c r="C36" s="96" t="inlineStr">
-        <is>
-          <t>(245)</t>
+      <c r="C36" s="95" t="inlineStr">
+        <is>
+          <t>(191)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="94" t="inlineStr">
-        <is>
-          <t>$172-$196</t>
-        </is>
-      </c>
-      <c r="B37" s="95" t="inlineStr">
-        <is>
-          <t>███████████████████████████</t>
-        </is>
-      </c>
-      <c r="C37" s="96" t="inlineStr">
-        <is>
-          <t>(170)</t>
+      <c r="A37" s="93" t="inlineStr">
+        <is>
+          <t>$210-$237</t>
+        </is>
+      </c>
+      <c r="B37" s="94" t="inlineStr">
+        <is>
+          <t>███████████████████████████████████</t>
+        </is>
+      </c>
+      <c r="C37" s="95" t="inlineStr">
+        <is>
+          <t>(169)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="94" t="inlineStr">
-        <is>
-          <t>$196-$219</t>
-        </is>
-      </c>
-      <c r="B38" s="95" t="inlineStr">
-        <is>
-          <t>██████████████████</t>
-        </is>
-      </c>
-      <c r="C38" s="96" t="inlineStr">
-        <is>
-          <t>(112)</t>
+      <c r="A38" s="93" t="inlineStr">
+        <is>
+          <t>$237-$264</t>
+        </is>
+      </c>
+      <c r="B38" s="94" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████</t>
+        </is>
+      </c>
+      <c r="C38" s="95" t="inlineStr">
+        <is>
+          <t>(165)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="94" t="inlineStr">
-        <is>
-          <t>$219-$243</t>
-        </is>
-      </c>
-      <c r="B39" s="95" t="inlineStr">
-        <is>
-          <t>█████████</t>
-        </is>
-      </c>
-      <c r="C39" s="96" t="inlineStr">
-        <is>
-          <t>(61)</t>
+      <c r="A39" s="93" t="inlineStr">
+        <is>
+          <t>$264-$290</t>
+        </is>
+      </c>
+      <c r="B39" s="94" t="inlineStr">
+        <is>
+          <t>█████████████████</t>
+        </is>
+      </c>
+      <c r="C39" s="95" t="inlineStr">
+        <is>
+          <t>(85)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="94" t="inlineStr">
-        <is>
-          <t>$243-$266</t>
-        </is>
-      </c>
-      <c r="B40" s="95" t="inlineStr">
-        <is>
-          <t>███████</t>
-        </is>
-      </c>
-      <c r="C40" s="96" t="inlineStr">
-        <is>
-          <t>(44)</t>
+      <c r="A40" s="93" t="inlineStr">
+        <is>
+          <t>$290-$317</t>
+        </is>
+      </c>
+      <c r="B40" s="94" t="inlineStr">
+        <is>
+          <t>███████████████</t>
+        </is>
+      </c>
+      <c r="C40" s="95" t="inlineStr">
+        <is>
+          <t>(74)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="94" t="inlineStr">
-        <is>
-          <t>$266-$289</t>
-        </is>
-      </c>
-      <c r="B41" s="95" t="inlineStr">
+      <c r="A41" s="93" t="inlineStr">
+        <is>
+          <t>$317-$344</t>
+        </is>
+      </c>
+      <c r="B41" s="94" t="inlineStr">
+        <is>
+          <t>████████</t>
+        </is>
+      </c>
+      <c r="C41" s="95" t="inlineStr">
+        <is>
+          <t>(42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="93" t="inlineStr">
+        <is>
+          <t>$344-$371</t>
+        </is>
+      </c>
+      <c r="B42" s="94" t="inlineStr">
+        <is>
+          <t>██████</t>
+        </is>
+      </c>
+      <c r="C42" s="95" t="inlineStr">
+        <is>
+          <t>(33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="93" t="inlineStr">
+        <is>
+          <t>$371-$397</t>
+        </is>
+      </c>
+      <c r="B43" s="94" t="inlineStr">
         <is>
           <t>█████</t>
         </is>
       </c>
-      <c r="C41" s="96" t="inlineStr">
-        <is>
-          <t>(34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="94" t="inlineStr">
-        <is>
-          <t>$289-$313</t>
-        </is>
-      </c>
-      <c r="B42" s="95" t="inlineStr">
+      <c r="C43" s="95" t="inlineStr">
+        <is>
+          <t>(24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="93" t="inlineStr">
+        <is>
+          <t>$397-$424</t>
+        </is>
+      </c>
+      <c r="B44" s="94" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="C44" s="95" t="inlineStr">
+        <is>
+          <t>(11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="93" t="inlineStr">
+        <is>
+          <t>$424-$451</t>
+        </is>
+      </c>
+      <c r="B45" s="94" t="inlineStr">
         <is>
           <t>█</t>
         </is>
       </c>
-      <c r="C42" s="96" t="inlineStr">
-        <is>
-          <t>(12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="94" t="inlineStr">
-        <is>
-          <t>$313-$336</t>
-        </is>
-      </c>
-      <c r="B43" s="95" t="inlineStr"/>
-      <c r="C43" s="96" t="inlineStr">
-        <is>
-          <t>(6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="94" t="inlineStr">
-        <is>
-          <t>$336-$360</t>
-        </is>
-      </c>
-      <c r="B44" s="95" t="inlineStr"/>
-      <c r="C44" s="96" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="94" t="inlineStr">
-        <is>
-          <t>$360-$383</t>
-        </is>
-      </c>
-      <c r="B45" s="95" t="inlineStr"/>
-      <c r="C45" s="96" t="inlineStr">
+      <c r="C45" s="95" t="inlineStr">
+        <is>
+          <t>(7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="93" t="inlineStr">
+        <is>
+          <t>$451-$477</t>
+        </is>
+      </c>
+      <c r="B46" s="94" t="inlineStr"/>
+      <c r="C46" s="95" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="93" t="inlineStr">
+        <is>
+          <t>$477-$504</t>
+        </is>
+      </c>
+      <c r="B47" s="94" t="inlineStr"/>
+      <c r="C47" s="95" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="94" t="inlineStr">
-        <is>
-          <t>$383-$407</t>
-        </is>
-      </c>
-      <c r="B46" s="95" t="inlineStr"/>
-      <c r="C46" s="96" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="93" t="inlineStr">
+        <is>
+          <t>$504-$531</t>
+        </is>
+      </c>
+      <c r="B48" s="94" t="inlineStr"/>
+      <c r="C48" s="95" t="inlineStr">
+        <is>
+          <t>(0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="93" t="inlineStr">
+        <is>
+          <t>$531-$558</t>
+        </is>
+      </c>
+      <c r="B49" s="94" t="inlineStr"/>
+      <c r="C49" s="95" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="94" t="inlineStr">
-        <is>
-          <t>$407-$430</t>
-        </is>
-      </c>
-      <c r="B47" s="95" t="inlineStr"/>
-      <c r="C47" s="96" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="93" t="inlineStr">
+        <is>
+          <t>$558-$584</t>
+        </is>
+      </c>
+      <c r="B50" s="94" t="inlineStr"/>
+      <c r="C50" s="95" t="inlineStr">
+        <is>
+          <t>(0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="93" t="inlineStr">
+        <is>
+          <t>$584-$611</t>
+        </is>
+      </c>
+      <c r="B51" s="94" t="inlineStr"/>
+      <c r="C51" s="95" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="93" t="inlineStr">
+        <is>
+          <t>$611-$638</t>
+        </is>
+      </c>
+      <c r="B52" s="94" t="inlineStr"/>
+      <c r="C52" s="95" t="inlineStr">
         <is>
           <t>(2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="94" t="inlineStr">
-        <is>
-          <t>$430-$454</t>
-        </is>
-      </c>
-      <c r="B48" s="95" t="inlineStr"/>
-      <c r="C48" s="96" t="inlineStr">
-        <is>
-          <t>(0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="94" t="inlineStr">
-        <is>
-          <t>$454-$477</t>
-        </is>
-      </c>
-      <c r="B49" s="95" t="inlineStr"/>
-      <c r="C49" s="96" t="inlineStr">
-        <is>
-          <t>(0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="94" t="inlineStr">
-        <is>
-          <t>$477-$500</t>
-        </is>
-      </c>
-      <c r="B50" s="95" t="inlineStr"/>
-      <c r="C50" s="96" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="94" t="inlineStr">
-        <is>
-          <t>$500-$524</t>
-        </is>
-      </c>
-      <c r="B51" s="95" t="inlineStr"/>
-      <c r="C51" s="96" t="inlineStr">
-        <is>
-          <t>(0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="94" t="inlineStr">
-        <is>
-          <t>$524-$547</t>
-        </is>
-      </c>
-      <c r="B52" s="95" t="inlineStr"/>
-      <c r="C52" s="96" t="inlineStr">
-        <is>
-          <t>(1)</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7644,226 +7817,220 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
-        </is>
-      </c>
-      <c r="C4" s="152" t="n">
-        <v>1702.714146816</v>
-      </c>
-      <c r="D4" s="136" t="n">
-        <v>357.895</v>
-      </c>
-      <c r="E4" s="153" t="n">
-        <v>45.475857</v>
-      </c>
-      <c r="F4" s="153" t="n">
-        <v>45.475857</v>
-      </c>
-      <c r="G4" s="153" t="n">
-        <v>33.447</v>
-      </c>
-      <c r="H4" s="153" t="n">
-        <v>19.10929</v>
-      </c>
-      <c r="I4" s="153" t="n">
-        <v>19.541</v>
-      </c>
-      <c r="J4" s="153" t="n">
-        <v>17.110245</v>
-      </c>
-      <c r="K4" s="50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L4" s="49" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="M4" s="49" t="n">
-        <v>0.75515</v>
-      </c>
-      <c r="N4" s="49" t="n">
-        <v>0.5430700000000001</v>
-      </c>
-      <c r="O4" s="49" t="n">
-        <v>0.42944</v>
-      </c>
-      <c r="P4" s="49" t="n">
-        <v>0.44245</v>
-      </c>
-      <c r="Q4" s="49" t="n">
-        <v>0.0073</v>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="C4" s="151" t="n">
+        <v>931.849371648</v>
+      </c>
+      <c r="D4" s="135" t="n">
+        <v>570.8200000000001</v>
+      </c>
+      <c r="E4" s="134" t="n">
+        <v>154.27568</v>
+      </c>
+      <c r="G4" s="134" t="n">
+        <v>96.529</v>
+      </c>
+      <c r="H4" s="134" t="n">
+        <v>22.560207</v>
+      </c>
+      <c r="I4" s="134" t="n">
+        <v>22.346</v>
+      </c>
+      <c r="J4" s="134" t="n">
+        <v>13.857882</v>
+      </c>
+      <c r="K4" s="51" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L4" s="50" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="M4" s="50" t="n">
+        <v>0.55724</v>
+      </c>
+      <c r="N4" s="50" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="O4" s="50" t="n">
+        <v>0.15577</v>
+      </c>
+      <c r="P4" s="50" t="n">
+        <v>0.10196</v>
+      </c>
+      <c r="Q4" s="50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufactur</t>
-        </is>
-      </c>
-      <c r="C5" s="152" t="n">
-        <v>2224.530653184</v>
-      </c>
-      <c r="D5" s="136" t="n">
-        <v>428.91</v>
-      </c>
-      <c r="E5" s="153" t="n">
-        <v>31.841871</v>
-      </c>
-      <c r="F5" s="153" t="n">
-        <v>31.841871</v>
-      </c>
-      <c r="G5" s="153" t="n">
-        <v>4.858</v>
-      </c>
-      <c r="H5" s="153" t="n">
-        <v>0.5009649</v>
-      </c>
-      <c r="I5" s="153" t="n">
-        <v>3.466</v>
-      </c>
-      <c r="J5" s="153" t="n">
-        <v>88.28834000000001</v>
-      </c>
-      <c r="K5" s="50" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L5" s="49" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M5" s="49" t="n">
-        <v>0.6423</v>
-      </c>
-      <c r="N5" s="49" t="n">
-        <v>0.60344005</v>
-      </c>
-      <c r="O5" s="49" t="n">
-        <v>0.49923</v>
-      </c>
-      <c r="P5" s="49" t="n">
-        <v>0.39969003</v>
-      </c>
-      <c r="Q5" s="49" t="n">
-        <v>0.0098</v>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="C5" s="151" t="n">
+        <v>1652.869431296</v>
+      </c>
+      <c r="D5" s="135" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="E5" s="134" t="n">
+        <v>43.389725</v>
+      </c>
+      <c r="G5" s="134" t="n">
+        <v>32.306</v>
+      </c>
+      <c r="H5" s="134" t="n">
+        <v>18.54989</v>
+      </c>
+      <c r="I5" s="134" t="n">
+        <v>18.948</v>
+      </c>
+      <c r="J5" s="134" t="n">
+        <v>16.581266</v>
+      </c>
+      <c r="K5" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L5" s="50" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="M5" s="50" t="n">
+        <v>0.75515</v>
+      </c>
+      <c r="N5" s="50" t="n">
+        <v>0.5430700000000001</v>
+      </c>
+      <c r="O5" s="50" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="P5" s="50" t="n">
+        <v>0.44245</v>
+      </c>
+      <c r="Q5" s="50" t="n">
+        <v>0.0073</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="C6" s="152" t="n">
-        <v>779.621105664</v>
-      </c>
-      <c r="D6" s="136" t="n">
-        <v>477.57</v>
-      </c>
-      <c r="E6" s="153" t="n">
-        <v>116.197075</v>
-      </c>
-      <c r="F6" s="153" t="n">
-        <v>116.197075</v>
-      </c>
-      <c r="G6" s="153" t="n">
-        <v>80.60899999999999</v>
-      </c>
-      <c r="H6" s="153" t="n">
-        <v>18.874739</v>
-      </c>
-      <c r="I6" s="153" t="n">
-        <v>18.661</v>
-      </c>
-      <c r="J6" s="153" t="n">
-        <v>11.594037</v>
-      </c>
-      <c r="K6" s="50" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L6" s="49" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="M6" s="49" t="n">
-        <v>0.55724</v>
-      </c>
-      <c r="N6" s="49" t="n">
-        <v>0.1725</v>
-      </c>
-      <c r="O6" s="49" t="n">
-        <v>0.15577</v>
-      </c>
-      <c r="P6" s="49" t="n">
-        <v>0.10196</v>
+          <t>QUALCOMM Incorporated</t>
+        </is>
+      </c>
+      <c r="C6" s="151" t="n">
+        <v>184.330452992</v>
+      </c>
+      <c r="D6" s="135" t="n">
+        <v>172.62</v>
+      </c>
+      <c r="E6" s="134" t="n">
+        <v>20.476868</v>
+      </c>
+      <c r="F6" s="134" t="n">
+        <v>16.92909</v>
+      </c>
+      <c r="G6" s="134" t="n">
+        <v>15.689</v>
+      </c>
+      <c r="H6" s="134" t="n">
+        <v>4.1827693</v>
+      </c>
+      <c r="I6" s="134" t="n">
+        <v>4.272</v>
+      </c>
+      <c r="J6" s="134" t="n">
+        <v>6.5968585</v>
+      </c>
+      <c r="K6" s="51" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L6" s="50" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M6" s="50" t="n">
+        <v>0.54226</v>
+      </c>
+      <c r="N6" s="50" t="n">
+        <v>0.18528</v>
+      </c>
+      <c r="O6" s="50" t="n">
+        <v>0.21013</v>
+      </c>
+      <c r="P6" s="50" t="n">
+        <v>0.33754003</v>
+      </c>
+      <c r="Q6" s="50" t="n">
+        <v>0.0208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
-        </is>
-      </c>
-      <c r="C7" s="152" t="n">
-        <v>1148.12977152</v>
-      </c>
-      <c r="D7" s="136" t="n">
-        <v>1016.59</v>
-      </c>
-      <c r="E7" s="153" t="n">
-        <v>21.643389</v>
-      </c>
-      <c r="F7" s="153" t="n">
-        <v>21.643389</v>
-      </c>
-      <c r="G7" s="153" t="n">
-        <v>16.541</v>
-      </c>
-      <c r="H7" s="153" t="n">
-        <v>12.718278</v>
-      </c>
-      <c r="I7" s="153" t="n">
-        <v>12.501</v>
-      </c>
-      <c r="J7" s="153" t="n">
-        <v>11.394834</v>
-      </c>
-      <c r="K7" s="50" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L7" s="49" t="n">
-        <v>3.457</v>
-      </c>
-      <c r="M7" s="49" t="n">
-        <v>0.7256899999999999</v>
-      </c>
-      <c r="N7" s="49" t="n">
-        <v>0.80370003</v>
-      </c>
-      <c r="O7" s="49" t="n">
-        <v>0.55906</v>
-      </c>
-      <c r="P7" s="49" t="n">
-        <v>0.66638</v>
-      </c>
-      <c r="Q7" s="49" t="n">
-        <v>0.06</v>
+          <t>Marvell Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="151" t="n">
+        <v>220.43426816</v>
+      </c>
+      <c r="D7" s="135" t="n">
+        <v>245.28</v>
+      </c>
+      <c r="E7" s="134" t="n">
+        <v>80.68420999999999</v>
+      </c>
+      <c r="G7" s="134" t="n">
+        <v>75.93600000000001</v>
+      </c>
+      <c r="H7" s="134" t="n">
+        <v>23.325636</v>
+      </c>
+      <c r="I7" s="134" t="n">
+        <v>22.903</v>
+      </c>
+      <c r="J7" s="134" t="n">
+        <v>11.605393</v>
+      </c>
+      <c r="K7" s="51" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L7" s="50" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="M7" s="50" t="n">
+        <v>0.52216</v>
+      </c>
+      <c r="N7" s="50" t="n">
+        <v>0.16679001</v>
+      </c>
+      <c r="O7" s="50" t="n">
+        <v>0.27934998</v>
+      </c>
+      <c r="P7" s="50" t="n">
+        <v>0.16523</v>
+      </c>
+      <c r="Q7" s="50" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="8">
@@ -7872,44 +8039,52 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="E8" s="154" t="n">
-        <v>38.658864</v>
-      </c>
-      <c r="F8" s="154" t="n">
-        <v>38.658864</v>
-      </c>
-      <c r="G8" s="154" t="n">
-        <v>24.994</v>
-      </c>
-      <c r="H8" s="154" t="n">
-        <v>15.7965085</v>
-      </c>
-      <c r="I8" s="154" t="n">
-        <v>15.581</v>
-      </c>
-      <c r="J8" s="154" t="n">
-        <v>14.352141</v>
-      </c>
-      <c r="K8" s="100" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L8" s="101" t="n">
-        <v>0.6779999999999999</v>
-      </c>
-      <c r="M8" s="101" t="n">
-        <v>0.6839949999999999</v>
-      </c>
-      <c r="N8" s="101" t="n">
-        <v>0.573255025</v>
-      </c>
-      <c r="O8" s="101" t="n">
-        <v>0.464335</v>
-      </c>
-      <c r="P8" s="101" t="n">
-        <v>0.421070015</v>
-      </c>
-      <c r="Q8" s="101" t="n">
-        <v>0.0098</v>
+      <c r="E8" s="152" t="n">
+        <v>62.0369675</v>
+      </c>
+      <c r="F8" s="152" t="n">
+        <v>16.92909</v>
+      </c>
+      <c r="G8" s="152" t="n">
+        <v>54.121</v>
+      </c>
+      <c r="H8" s="152" t="n">
+        <v>20.5550485</v>
+      </c>
+      <c r="I8" s="152" t="n">
+        <v>20.647</v>
+      </c>
+      <c r="J8" s="152" t="n">
+        <v>12.7316375</v>
+      </c>
+      <c r="K8" s="98" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="L8" s="99" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="M8" s="99" t="n">
+        <v>0.54975</v>
+      </c>
+      <c r="N8" s="99" t="n">
+        <v>0.17889</v>
+      </c>
+      <c r="O8" s="99" t="n">
+        <v>0.24473999</v>
+      </c>
+      <c r="P8" s="99" t="n">
+        <v>0.251385015</v>
+      </c>
+      <c r="Q8" s="99" t="n">
+        <v>0.01405</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>Forward P/E left blank where yfinance's forward EPS is implausibly far above trailing EPS: AMD, AVGO, MRVL. Trailing P/E is shown for those peers.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7923,7 +8098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7945,7 +8120,7 @@
     <row r="2">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Peers: AVGO, TSM, AMD, MU</t>
+          <t>Peers: AMD, AVGO, QCOM, MRVL</t>
         </is>
       </c>
     </row>
@@ -7953,18 +8128,18 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FORWARD METRICS ($M)</t>
+          <t>TRAILING METRICS ($M)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NTM EPS (Trailing Margin)</t>
-        </is>
-      </c>
-      <c r="B5" s="136" t="n">
-        <v>12.29</v>
+          <t>TTM EPS</t>
+        </is>
+      </c>
+      <c r="B5" s="135" t="n">
+        <v>7.94</v>
       </c>
     </row>
     <row r="6">
@@ -7973,38 +8148,38 @@
           <t>Normalized EPS (Mid-Cycle Avg Margin)</t>
         </is>
       </c>
-      <c r="B6" s="136" t="n">
-        <v>4.98</v>
+      <c r="B6" s="135" t="n">
+        <v>3.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NTM EBITDA (Projected OpInc + D&amp;A)</t>
-        </is>
-      </c>
-      <c r="B7" s="51" t="n">
-        <v>313689.1</v>
+          <t>TTM EBITDA (OpInc + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n">
+        <v>201266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NTM EBIT (Operating Income)</t>
-        </is>
-      </c>
-      <c r="B8" s="51" t="n">
-        <v>310002.1</v>
+          <t>TTM EBIT (Operating Income)</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="n">
+        <v>197579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NTM Revenue (Projected)</t>
-        </is>
-      </c>
-      <c r="B9" s="51" t="n">
-        <v>454453.5</v>
+          <t>TTM Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>302969</v>
       </c>
     </row>
     <row r="10">
@@ -8013,7 +8188,7 @@
           <t>TTM Free Cash Flow</t>
         </is>
       </c>
-      <c r="B10" s="51" t="n">
+      <c r="B10" s="52" t="n">
         <v>127006</v>
       </c>
     </row>
@@ -8023,7 +8198,7 @@
           <t>FCF Yield (TTM FCF / EV)</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="50" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8033,7 +8208,7 @@
           <t>Shares Outstanding (M)</t>
         </is>
       </c>
-      <c r="B12" s="152" t="n">
+      <c r="B12" s="151" t="n">
         <v>24285</v>
       </c>
     </row>
@@ -8043,7 +8218,7 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B13" s="51" t="n">
+      <c r="B13" s="52" t="n">
         <v>22443</v>
       </c>
     </row>
@@ -8053,7 +8228,7 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="B14" s="51" t="n">
+      <c r="B14" s="52" t="n">
         <v>33366</v>
       </c>
     </row>
@@ -8063,7 +8238,7 @@
           <t>Book Value (Stockholders' Equity)</t>
         </is>
       </c>
-      <c r="B15" s="51" t="n">
+      <c r="B15" s="52" t="n">
         <v>228984</v>
       </c>
     </row>
@@ -8073,7 +8248,7 @@
           <t>Book Value Per Share</t>
         </is>
       </c>
-      <c r="B16" s="136" t="n">
+      <c r="B16" s="135" t="n">
         <v>9.43</v>
       </c>
     </row>
@@ -8083,8 +8258,8 @@
           <t>Price / Book</t>
         </is>
       </c>
-      <c r="B17" s="155" t="n">
-        <v>24.43</v>
+      <c r="B17" s="153" t="n">
+        <v>23.47</v>
       </c>
     </row>
     <row r="18">
@@ -8093,7 +8268,7 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B18" s="51" t="n">
+      <c r="B18" s="52" t="n">
         <v>31575</v>
       </c>
     </row>
@@ -8103,7 +8278,7 @@
           <t>Inventory Turnover (COGS / Inv)</t>
         </is>
       </c>
-      <c r="B19" s="153" t="n">
+      <c r="B19" s="134" t="n">
         <v>2.43</v>
       </c>
     </row>
@@ -8113,436 +8288,386 @@
           <t>Days Inventory Outstanding</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n">
+      <c r="B20" s="52" t="n">
         <v>150.2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>P/E EPS Basis - Trailing EPS (peer fwd P/E gated to trailing)</t>
-        </is>
-      </c>
-      <c r="B21" s="136" t="n">
-        <v>7.94</v>
-      </c>
-    </row>
-    <row r="22"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>DUPONT ROE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>DUPONT ROE DECOMPOSITION</t>
-        </is>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Net Profit Margin (NI / Revenue)</t>
+        </is>
+      </c>
+      <c r="B23" s="50" t="n">
+        <v>0.6366000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net Profit Margin (NI / Revenue)</t>
-        </is>
-      </c>
-      <c r="B24" s="49" t="n">
-        <v>0.6366000000000001</v>
+          <t>Asset Turnover (Revenue / Assets)</t>
+        </is>
+      </c>
+      <c r="B24" s="153" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Asset Turnover (Revenue / Assets)</t>
-        </is>
-      </c>
-      <c r="B25" s="155" t="n">
-        <v>0.946</v>
+          <t>Equity Multiplier (Assets / Equity)</t>
+        </is>
+      </c>
+      <c r="B25" s="153" t="n">
+        <v>1.3987</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equity Multiplier (Assets / Equity)</t>
-        </is>
-      </c>
-      <c r="B26" s="155" t="n">
-        <v>1.3987</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
           <t>Return on Equity (ROE)</t>
         </is>
       </c>
-      <c r="B27" s="55" t="n">
+      <c r="B26" s="57" t="n">
         <v>0.8423</v>
       </c>
     </row>
-    <row r="28"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC REVENUE SPLIT</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>GEOGRAPHIC REVENUE SPLIT</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n">
+        <v>0.6929</v>
+      </c>
+      <c r="C29" s="101" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B30" s="49" t="n">
-        <v>0.6929</v>
-      </c>
-      <c r="C30" s="103" t="inlineStr">
-        <is>
-          <t>████████████████████</t>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n">
+        <v>0.1961</v>
+      </c>
+      <c r="C30" s="101" t="inlineStr">
+        <is>
+          <t>█████</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B31" s="49" t="n">
-        <v>0.1961</v>
-      </c>
-      <c r="C31" s="103" t="inlineStr">
-        <is>
-          <t>█████</t>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="C31" s="101" t="inlineStr">
+        <is>
+          <t>██</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B32" s="49" t="n">
-        <v>0.0911</v>
-      </c>
-      <c r="C32" s="103" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B33" s="49" t="n">
+      <c r="B32" s="50" t="n">
         <v>0.0199</v>
       </c>
-      <c r="C33" s="103" t="inlineStr"/>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="C32" s="101" t="inlineStr"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>US / International</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>69% / 31%</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER CONCENTRATION</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+    </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>CUSTOMER CONCENTRATION</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="n"/>
+      <c r="A37" s="102" t="inlineStr">
+        <is>
+          <t>Status: CONCENTRATED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="104" t="inlineStr">
-        <is>
-          <t>Status: CONCENTRATED</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  22% of total revenue</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22% of total revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>14% of total revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42" ht="52" customHeight="1">
-      <c r="A42" s="105" t="inlineStr">
-        <is>
-          <t>For fiscal year 2026, sales to one direct customer represented 22% of total revenue and sales to another direct customer represented 14% of total revenue, all of which were primarily attributable to the Compute &amp; Networking segment. 40 Table of Contents Concentration of Revenue We refer to customers who purchase products directly from NVIDIA as direct customers, such as AIBs, distributors, ODMs, OEMs, CSPs, AI model makers, and system integrators. Direct Customers – For fiscal year 2026, sale...</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
+          <t xml:space="preserve">  14% of total revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="52" customHeight="1">
+      <c r="A41" s="103" t="inlineStr">
+        <is>
+          <t>For fiscal year 2026, sales to one direct customer represented 22% of total revenue and sales to another direct customer represented 14% of total revenue, all of which were primarily attributable to the Compute &amp; Networking segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION BY MULTIPLES</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>VALUATION BY MULTIPLES</t>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Low Multiple</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Mid Multiple</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>High Multiple</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Low Price</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>Mid Price</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>High Price</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>Low Multiple</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Mid Multiple</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>High Multiple</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>Low Price</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>Mid Price</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>High Price</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P/E (trailing)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Not priced - see note below</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Forward P/E</t>
-        </is>
-      </c>
-      <c r="B46" s="156" t="n">
-        <v>27.06559035</v>
-      </c>
-      <c r="C46" s="156" t="n">
-        <v>31.841871</v>
-      </c>
-      <c r="D46" s="156" t="n">
-        <v>36.61815165</v>
-      </c>
-      <c r="E46" s="157">
-        <f>$B$21*B46</f>
-        <v/>
-      </c>
-      <c r="F46" s="157">
-        <f>$B$21*C46</f>
-        <v/>
-      </c>
-      <c r="G46" s="157">
-        <f>$B$21*D46</f>
-        <v/>
+          <t>EV/EBITDA (trailing)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Not priced - see note below</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B47" s="156" t="n">
-        <v>28.42995</v>
-      </c>
-      <c r="C47" s="156" t="n">
-        <v>33.447</v>
-      </c>
-      <c r="D47" s="156" t="n">
-        <v>38.46405</v>
-      </c>
-      <c r="E47" s="157">
-        <f>IF($B$12&lt;&gt;0,($B$7*B47-$B$14+$B$13)/$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="F47" s="157">
-        <f>IF($B$12&lt;&gt;0,($B$7*C47-$B$14+$B$13)/$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="157">
-        <f>IF($B$12&lt;&gt;0,($B$7*D47-$B$14+$B$13)/$B$12,0)</f>
+          <t>EV/Revenue (trailing)</t>
+        </is>
+      </c>
+      <c r="B47" s="154" t="n">
+        <v>18.948</v>
+      </c>
+      <c r="C47" s="154" t="n">
+        <v>22.346</v>
+      </c>
+      <c r="D47" s="154" t="n">
+        <v>22.903</v>
+      </c>
+      <c r="E47" s="155">
+        <f>IF($B$12&lt;&gt;0,($B$9*B47-$B$14+$B$13)/$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F47" s="155">
+        <f>IF($B$12&lt;&gt;0,($B$9*C47-$B$14+$B$13)/$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="155">
+        <f>IF($B$12&lt;&gt;0,($B$9*D47-$B$14+$B$13)/$B$12,0)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>EV/Revenue</t>
-        </is>
-      </c>
-      <c r="B48" s="156" t="n">
-        <v>15.86185</v>
-      </c>
-      <c r="C48" s="156" t="n">
-        <v>18.661</v>
-      </c>
-      <c r="D48" s="156" t="n">
-        <v>21.46015</v>
-      </c>
-      <c r="E48" s="157">
-        <f>IF($B$12&lt;&gt;0,($B$9*B48-$B$14+$B$13)/$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="F48" s="157">
-        <f>IF($B$12&lt;&gt;0,($B$9*C48-$B$14+$B$13)/$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="G48" s="157">
-        <f>IF($B$12&lt;&gt;0,($B$9*D48-$B$14+$B$13)/$B$12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>Low / Mid / High = lowest / median / highest peer multiple. Outliers below 0.4x or above 2.5x the median are excluded only when 3+ peers report it, 2+ remain, and no other peer sits within 2x of the outlier (a cluster is kept). Peer multiples are trailing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>EV/Revenue: AVGO 18.9x, AMD 22.3x, MRVL 22.9x (outliers excluded: QCOM 4.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Current Market Price</t>
         </is>
       </c>
-      <c r="B50" s="158" t="n">
-        <v>230.36</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="B51" s="156" t="n">
+        <v>221.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>Premium / Discount to Mid</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Forward P/E</t>
-        </is>
-      </c>
-      <c r="B52" s="109">
-        <f>IF(B50&lt;&gt;0,F46/B50-1,0)</f>
-        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B53" s="109">
-        <f>IF(B50&lt;&gt;0,F47/B50-1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>EV/Revenue</t>
-        </is>
-      </c>
-      <c r="B54" s="109">
-        <f>IF(B50&lt;&gt;0,F48/B50-1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55"/>
+          <t>EV/Revenue (trailing)</t>
+        </is>
+      </c>
+      <c r="B53" s="107">
+        <f>IF(B51&lt;&gt;0,F47/B51-1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION RANGE SUMMARY</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>VALUATION RANGE SUMMARY</t>
-        </is>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Overall Low</t>
+        </is>
+      </c>
+      <c r="B56" s="143">
+        <f>MIN(E47)</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Overall Low</t>
-        </is>
-      </c>
-      <c r="B57" s="144">
-        <f>MIN(E46,E47,E48)</f>
+          <t>Overall Mid (Average)</t>
+        </is>
+      </c>
+      <c r="B57" s="143">
+        <f>AVERAGE(F47)</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Overall Mid (Average)</t>
-        </is>
-      </c>
-      <c r="B58" s="144">
-        <f>AVERAGE(F46,F47,F48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
           <t>Overall High</t>
         </is>
       </c>
-      <c r="B59" s="144">
-        <f>MAX(G46,G47,G48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60"/>
+      <c r="B58" s="143">
+        <f>MAX(G47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>METHOD RELEVANCE NOTES</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>METHOD RELEVANCE NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Preferred Method</t>
         </is>
       </c>
-      <c r="B62" s="110" t="inlineStr">
-        <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="111" t="inlineStr">
-        <is>
-          <t>CAUTION: NVDA has 65% operating margins. EV/Revenue undervalues high-margin businesses because it ignores profitability. Weight EV/EBITDA and P/E more heavily.</t>
+      <c r="B61" s="108" t="inlineStr">
+        <is>
+          <t>EV/Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="39" customHeight="1">
+      <c r="A62" s="109" t="inlineStr">
+        <is>
+          <t>NVDA earns a 65% operating margin against peers at 17%-54%. A peer revenue multiple ignores that profit, so treat this EV/Revenue result as conservative. EV/EBITDA and P/E are not priced here: peer earnings multiples are inflated by thinner peer margins and do not transfer to NVDA.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8582,42 +8707,42 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="162" t="inlineStr">
+      <c r="A4" s="158" t="inlineStr">
         <is>
           <t>1) AI% of Capex (per hyperscaler)</t>
         </is>
       </c>
-      <c r="B4" s="163" t="n"/>
-      <c r="C4" s="163" t="n"/>
-      <c r="D4" s="163" t="n"/>
-      <c r="E4" s="163" t="n"/>
-      <c r="F4" s="163" t="n"/>
-      <c r="G4" s="163" t="n"/>
+      <c r="B4" s="159" t="n"/>
+      <c r="C4" s="159" t="n"/>
+      <c r="D4" s="159" t="n"/>
+      <c r="E4" s="159" t="n"/>
+      <c r="F4" s="159" t="n"/>
+      <c r="G4" s="159" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="164" t="inlineStr">
+      <c r="A5" s="160" t="inlineStr">
         <is>
           <t>Hyperscaler</t>
         </is>
       </c>
-      <c r="B5" s="164" t="inlineStr">
+      <c r="B5" s="160" t="inlineStr">
         <is>
           <t>AI %</t>
         </is>
       </c>
-      <c r="C5" s="164" t="inlineStr">
+      <c r="C5" s="160" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D5" s="164" t="inlineStr">
+      <c r="D5" s="160" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E5" s="164" t="inlineStr"/>
-      <c r="F5" s="164" t="inlineStr"/>
-      <c r="G5" s="164" t="inlineStr">
+      <c r="E5" s="160" t="inlineStr"/>
+      <c r="F5" s="160" t="inlineStr"/>
+      <c r="G5" s="160" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
@@ -8629,17 +8754,17 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B6" s="165" t="n">
+      <c r="B6" s="161" t="n">
         <v>0.7</v>
       </c>
-      <c r="C6" s="166" t="inlineStr">
+      <c r="C6" s="162" t="inlineStr">
         <is>
           <t>Q3 FY26 earnings 8-K (Apr 29 2026)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Q3 FY26 (period ending ); capex commentary tied to Azure AI infrastructure expansion. ~70% AI-attributable per mgmt commentary on</t>
+          <t>Q3 FY26; capex commentary tied to Azure AI infrastructure expansion. ~70% AI-attributable per mgmt commentary on</t>
         </is>
       </c>
     </row>
@@ -8649,10 +8774,10 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B7" s="165" t="n">
+      <c r="B7" s="161" t="n">
         <v>0.8</v>
       </c>
-      <c r="C7" s="166" t="inlineStr">
+      <c r="C7" s="162" t="inlineStr">
         <is>
           <t>Q1 CY26 earnings 8-K (Apr 29 2026)</t>
         </is>
@@ -8669,10 +8794,10 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B8" s="165" t="n">
+      <c r="B8" s="161" t="n">
         <v>0.65</v>
       </c>
-      <c r="C8" s="166" t="inlineStr">
+      <c r="C8" s="162" t="inlineStr">
         <is>
           <t>Q1 CY26 earnings 8-K (Apr 29 2026)</t>
         </is>
@@ -8689,10 +8814,10 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B9" s="165" t="n">
+      <c r="B9" s="161" t="n">
         <v>0.45</v>
       </c>
-      <c r="C9" s="166" t="inlineStr">
+      <c r="C9" s="162" t="inlineStr">
         <is>
           <t>Q1 CY26 earnings 8-K (Apr 29 2026)</t>
         </is>
@@ -8709,10 +8834,10 @@
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B10" s="165" t="n">
+      <c r="B10" s="161" t="n">
         <v>0.8</v>
       </c>
-      <c r="C10" s="166" t="inlineStr">
+      <c r="C10" s="162" t="inlineStr">
         <is>
           <t>Q3 FY26 earnings 8-K (Mar 10 2026)</t>
         </is>
@@ -8725,53 +8850,49 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Yellow cells are editable.</t>
-        </is>
-      </c>
+      <c r="A12" s="4" t="n"/>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="162" t="inlineStr">
+      <c r="A14" s="158" t="inlineStr">
         <is>
           <t>2) Hyperscaler Capex TTM ($M)</t>
         </is>
       </c>
-      <c r="B14" s="163" t="n"/>
-      <c r="C14" s="163" t="n"/>
-      <c r="D14" s="163" t="n"/>
-      <c r="E14" s="163" t="n"/>
-      <c r="F14" s="163" t="n"/>
-      <c r="G14" s="163" t="n"/>
+      <c r="B14" s="159" t="n"/>
+      <c r="C14" s="159" t="n"/>
+      <c r="D14" s="159" t="n"/>
+      <c r="E14" s="159" t="n"/>
+      <c r="F14" s="159" t="n"/>
+      <c r="G14" s="159" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="164" t="inlineStr">
+      <c r="A15" s="160" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B15" s="164" t="inlineStr">
+      <c r="B15" s="160" t="inlineStr">
         <is>
           <t>Prior TTM</t>
         </is>
       </c>
-      <c r="C15" s="164" t="inlineStr">
+      <c r="C15" s="160" t="inlineStr">
         <is>
           <t>Current TTM</t>
         </is>
       </c>
-      <c r="D15" s="164" t="inlineStr">
+      <c r="D15" s="160" t="inlineStr">
         <is>
           <t>YoY</t>
         </is>
       </c>
-      <c r="E15" s="164" t="inlineStr">
+      <c r="E15" s="160" t="inlineStr">
         <is>
           <t>AI %</t>
         </is>
       </c>
-      <c r="F15" s="164" t="inlineStr">
+      <c r="F15" s="160" t="inlineStr">
         <is>
           <t>AI Capex (TTM)</t>
         </is>
@@ -8783,19 +8904,19 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B16" s="51" t="n">
+      <c r="B16" s="52" t="n">
         <v>64551</v>
       </c>
-      <c r="C16" s="167" t="n">
+      <c r="C16" s="163" t="n">
         <v>115948</v>
       </c>
-      <c r="D16" s="168" t="n">
+      <c r="D16" s="164" t="n">
         <v>0.7962231413920776</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="50" t="n">
         <v>0.7</v>
       </c>
-      <c r="F16" s="51" t="n">
+      <c r="F16" s="52" t="n">
         <v>81163.60000000001</v>
       </c>
     </row>
@@ -8805,19 +8926,19 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B17" s="51" t="n">
+      <c r="B17" s="52" t="n">
         <v>52162</v>
       </c>
-      <c r="C17" s="167" t="n">
+      <c r="C17" s="163" t="n">
         <v>89325</v>
       </c>
-      <c r="D17" s="168" t="n">
+      <c r="D17" s="164" t="n">
         <v>0.7124535102181665</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="50" t="n">
         <v>0.8</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="52" t="n">
         <v>71460</v>
       </c>
     </row>
@@ -8827,19 +8948,19 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B18" s="51" t="n">
+      <c r="B18" s="52" t="n">
         <v>66980</v>
       </c>
-      <c r="C18" s="167" t="n">
+      <c r="C18" s="163" t="n">
         <v>132402</v>
       </c>
-      <c r="D18" s="168" t="n">
+      <c r="D18" s="164" t="n">
         <v>0.976739325171693</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="50" t="n">
         <v>0.65</v>
       </c>
-      <c r="F18" s="51" t="n">
+      <c r="F18" s="52" t="n">
         <v>86061.3</v>
       </c>
     </row>
@@ -8849,19 +8970,19 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B19" s="51" t="n">
+      <c r="B19" s="52" t="n">
         <v>107656</v>
       </c>
-      <c r="C19" s="167" t="n">
+      <c r="C19" s="163" t="n">
         <v>173028</v>
       </c>
-      <c r="D19" s="168" t="n">
+      <c r="D19" s="164" t="n">
         <v>0.6072304376904213</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="50" t="n">
         <v>0.45</v>
       </c>
-      <c r="F19" s="51" t="n">
+      <c r="F19" s="52" t="n">
         <v>77862.60000000001</v>
       </c>
     </row>
@@ -8871,105 +8992,105 @@
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n">
-        <v>21215</v>
-      </c>
-      <c r="C20" s="167" t="n">
-        <v>55663</v>
-      </c>
-      <c r="D20" s="168" t="n">
-        <v>1.623756775866132</v>
-      </c>
-      <c r="E20" s="49" t="n">
+      <c r="B20" s="52" t="n">
+        <v>27414</v>
+      </c>
+      <c r="C20" s="163" t="n">
+        <v>75660</v>
+      </c>
+      <c r="D20" s="164" t="n">
+        <v>1.759903698840009</v>
+      </c>
+      <c r="E20" s="50" t="n">
         <v>0.8</v>
       </c>
-      <c r="F20" s="51" t="n">
-        <v>44530.4</v>
+      <c r="F20" s="52" t="n">
+        <v>60528</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="164" t="inlineStr">
+      <c r="A21" s="160" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="169" t="n">
-        <v>312564</v>
-      </c>
-      <c r="C21" s="169" t="n">
-        <v>566366</v>
-      </c>
-      <c r="D21" s="170" t="n">
-        <v>0.8120001023790328</v>
-      </c>
-      <c r="E21" s="171" t="n">
-        <v>0.6375345624560796</v>
-      </c>
-      <c r="F21" s="169" t="n">
-        <v>361077.9</v>
+      <c r="B21" s="165" t="n">
+        <v>318763</v>
+      </c>
+      <c r="C21" s="165" t="n">
+        <v>586363</v>
+      </c>
+      <c r="D21" s="166" t="n">
+        <v>0.8394951735301776</v>
+      </c>
+      <c r="E21" s="167" t="n">
+        <v>0.6430751940350943</v>
+      </c>
+      <c r="F21" s="165" t="n">
+        <v>377075.5</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="162" t="inlineStr">
+      <c r="A23" s="158" t="inlineStr">
         <is>
           <t>3) NVDA DC Revenue Decomposition (TTM)</t>
         </is>
       </c>
-      <c r="B23" s="163" t="n"/>
-      <c r="C23" s="163" t="n"/>
-      <c r="D23" s="163" t="n"/>
-      <c r="E23" s="163" t="n"/>
-      <c r="F23" s="163" t="n"/>
-      <c r="G23" s="163" t="n"/>
+      <c r="B23" s="159" t="n"/>
+      <c r="C23" s="159" t="n"/>
+      <c r="D23" s="159" t="n"/>
+      <c r="E23" s="159" t="n"/>
+      <c r="F23" s="159" t="n"/>
+      <c r="G23" s="159" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="164" t="inlineStr">
+      <c r="B24" s="160" t="inlineStr">
         <is>
           <t>Prior TTM ($M)</t>
         </is>
       </c>
-      <c r="C24" s="164" t="inlineStr">
+      <c r="C24" s="160" t="inlineStr">
         <is>
           <t>Current TTM ($M)</t>
         </is>
       </c>
-      <c r="D24" s="164" t="inlineStr">
+      <c r="D24" s="160" t="inlineStr">
         <is>
           <t>YoY</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="172" t="inlineStr">
+      <c r="A25" s="168" t="inlineStr">
         <is>
           <t>Total hyperscaler capex</t>
         </is>
       </c>
-      <c r="B25" s="51" t="n">
-        <v>312564</v>
-      </c>
-      <c r="C25" s="51" t="n">
-        <v>566366</v>
-      </c>
-      <c r="D25" s="168" t="n">
-        <v>0.8120001023790328</v>
+      <c r="B25" s="52" t="n">
+        <v>318763</v>
+      </c>
+      <c r="C25" s="52" t="n">
+        <v>586363</v>
+      </c>
+      <c r="D25" s="164" t="n">
+        <v>0.8394951735301776</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="172" t="inlineStr">
-        <is>
-          <t>× weighted AI% → AI capex pool</t>
-        </is>
-      </c>
-      <c r="B26" s="51" t="n">
-        <v>195869.5</v>
-      </c>
-      <c r="C26" s="51" t="n">
-        <v>361077.9</v>
-      </c>
-      <c r="D26" s="168" t="n">
-        <v>0.8434615904977549</v>
+      <c r="A26" s="168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  × weighted AI% → AI capex pool</t>
+        </is>
+      </c>
+      <c r="B26" s="52" t="n">
+        <v>200828.7</v>
+      </c>
+      <c r="C26" s="52" t="n">
+        <v>377075.5</v>
+      </c>
+      <c r="D26" s="164" t="n">
+        <v>0.8775976740376251</v>
       </c>
     </row>
     <row r="27"/>
@@ -8979,7 +9100,7 @@
           <t>NVDA take rate (share of AI capex going to NVDA GPUs)</t>
         </is>
       </c>
-      <c r="C28" s="173" t="n">
+      <c r="C28" s="169" t="n">
         <v>0.4</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -8992,42 +9113,42 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>→ Hyperscaler-driven NVDA DC rev</t>
-        </is>
-      </c>
-      <c r="B30" s="169" t="n">
-        <v>78347.8</v>
-      </c>
-      <c r="C30" s="169" t="n">
-        <v>144431.16</v>
+          <t xml:space="preserve">  → Hyperscaler-driven NVDA DC rev</t>
+        </is>
+      </c>
+      <c r="B30" s="165" t="n">
+        <v>80331.48</v>
+      </c>
+      <c r="C30" s="165" t="n">
+        <v>150830.2</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="172" t="inlineStr">
-        <is>
-          <t>+ Non-hyperscaler NVDA DC rev</t>
-        </is>
-      </c>
-      <c r="B31" s="51" t="n">
-        <v>36838.2</v>
-      </c>
-      <c r="C31" s="51" t="n">
-        <v>133366.84</v>
-      </c>
-      <c r="D31" s="168" t="n">
-        <v>2.620340841843521</v>
+      <c r="A31" s="168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Non-hyperscaler NVDA DC rev</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n">
+        <v>34854.52</v>
+      </c>
+      <c r="C31" s="52" t="n">
+        <v>126967.8</v>
+      </c>
+      <c r="D31" s="164" t="n">
+        <v>2.642792957699604</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Total NVDA DC revenue (actual)</t>
-        </is>
-      </c>
-      <c r="B32" s="167" t="n">
+          <t xml:space="preserve">  Total NVDA DC revenue (actual)</t>
+        </is>
+      </c>
+      <c r="B32" s="163" t="n">
         <v>115186</v>
       </c>
-      <c r="C32" s="167" t="n">
+      <c r="C32" s="163" t="n">
         <v>277798</v>
       </c>
     </row>
@@ -9038,50 +9159,50 @@
           <t>Hyperscaler dependency ratio</t>
         </is>
       </c>
-      <c r="B34" s="49" t="n">
-        <v>0.6801850919382564</v>
-      </c>
-      <c r="C34" s="174" t="n">
-        <v>0.5199143262370499</v>
-      </c>
-      <c r="D34" s="168" t="n">
-        <v>-0.1602707657012065</v>
+      <c r="B34" s="50" t="n">
+        <v>0.6974066292778637</v>
+      </c>
+      <c r="C34" s="170" t="n">
+        <v>0.5429491932987278</v>
+      </c>
+      <c r="D34" s="164" t="n">
+        <v>-0.1544574359791359</v>
       </c>
     </row>
     <row r="35"/>
     <row r="36">
-      <c r="A36" s="162" t="inlineStr">
+      <c r="A36" s="158" t="inlineStr">
         <is>
           <t>4) Leading Indicator — YoY Capex vs NVDA DC</t>
         </is>
       </c>
-      <c r="B36" s="163" t="n"/>
-      <c r="C36" s="163" t="n"/>
-      <c r="D36" s="163" t="n"/>
-      <c r="E36" s="163" t="n"/>
-      <c r="F36" s="163" t="n"/>
-      <c r="G36" s="163" t="n"/>
+      <c r="B36" s="159" t="n"/>
+      <c r="C36" s="159" t="n"/>
+      <c r="D36" s="159" t="n"/>
+      <c r="E36" s="159" t="n"/>
+      <c r="F36" s="159" t="n"/>
+      <c r="G36" s="159" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="172" t="inlineStr">
+      <c r="A37" s="168" t="inlineStr">
         <is>
           <t>Hyperscaler AI capex growth (YoY)</t>
         </is>
       </c>
-      <c r="B37" s="168" t="n">
-        <v>0.8434615904977549</v>
+      <c r="B37" s="164" t="n">
+        <v>0.8775976740376251</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Leading indicator unavailable — need 8 quarters of capex data (have fewer). Will populate after next refresh.</t>
+          <t>Leading indicator unavailable — need 8 quarters of capex data (have fewer).</t>
         </is>
       </c>
     </row>
     <row r="39"/>
     <row r="40" ht="80" customHeight="1">
-      <c r="A40" s="175" t="inlineStr">
+      <c r="A40" s="171" t="inlineStr">
         <is>
           <t>How to read: Hyperscaler capex → AI capex → NVDA GPU revenue is a 1-2 quarter leading indicator. Hyperscalers guide capex on earnings calls before NVDA ships the silicon. Track the YoY gap each quarter: a negative gap (hyperscalers spending faster than NVDA ships) is the first observable sign of a supply-constrained upswing. A persistently positive gap (NVDA outgrowing hyperscaler capex) means non-hyperscaler demand is carrying the growth.</t>
         </is>
